--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>44463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>44587</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45663</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45911</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45646</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45336</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>46136</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>46157</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45303</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44823</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>45202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>45470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45714</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44463</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44463</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>45671</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44970</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>44700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>46213</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45244</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>45492</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45465</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45929</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>45315</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>45303</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>45089</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46091</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45716</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45016</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44476</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>46013</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45622</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44910</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44767</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45665</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45799</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>45602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>46091</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44460</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>44816</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45577</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44743</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45357</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45738</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44686</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45265</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44767</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45477</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45755</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45748</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>45328</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44767</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45938</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45945</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>46150</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45093</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45139</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45958</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45352</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45128</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45985</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45267</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45993</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45343</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45112</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45546</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45302</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>44971</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45946</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45845</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45468</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>46189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>46188</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45842</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45477</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>46108</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46134</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45247</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>46253</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44825</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45015</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45506</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45446</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>46279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45754</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45511</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45295</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45467</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45547</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45736</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>46058</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44468</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44536</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44670</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>44672</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44560</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44705</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>44558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44744</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44767</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44609</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44628</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44572</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44607</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44592</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>44623</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44837</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>44627</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44744</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>44461</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44491</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44596</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44862</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>44866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44470</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44767</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44838</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44713</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44522</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44749</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>44518</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44587</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44685</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44525</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44645</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44697</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44672</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44628</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45416</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45338</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>44601</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45112</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45474</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45121</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45520</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45144</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44645</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45643</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45665</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>44824</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45554</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45577</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45419</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45127</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45307</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44744</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45132</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45544</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45049</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45342</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45652</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45761</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45300</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>44634</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44961</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45693</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>44846</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45465</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45110</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45490</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45665</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44655</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45405</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45007</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45707</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45343</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45357</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45089</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45173</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45116</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45555</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45233</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45233</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45204</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45260</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45555</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44487</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45600</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45121</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45544</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44938</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45532</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45326</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45244</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45119</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>44627</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45586</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44513</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45229</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44984</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45496</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45000</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45561</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45532</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45343</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45343</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45532</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45338</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45577</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>44742</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44572</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45323</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45446</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44945</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45477</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45727</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45085</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44817</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44587</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45069</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45364</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45485</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44774</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45119</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45121</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45281</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45554</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45583</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44847</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45247</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46136</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45887</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44853</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45646</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45226</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45668</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>44855</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>44853</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45777</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45166</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45166</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>44595</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45470</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45027</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45749</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45889</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45144</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45144</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45331</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45338</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45755</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45895</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45083</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45894</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45035</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45644</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45159</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45896</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45898</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45900</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45887</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45355</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45887</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45083</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45900</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45198</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44544</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45900</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44846</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45482</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45589</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45900</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45577</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45737</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45554</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45533</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>46141</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45729</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45792</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45915</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45915</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45197</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45915</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45103</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45190</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44984</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44858</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45226</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45412</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44599</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45925</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45925</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45134</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45925</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44876</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>44915</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45366</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45315</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45467</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45247</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44995</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45930</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44795</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45933</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45002</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45755</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45328</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>44904</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45939</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45939</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>44847</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>46147</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45939</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45939</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45939</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45939</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45945</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45426</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45568</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>44918</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45945</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45945</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>46149</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45049</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45953</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45386</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45377</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35283,7 +35283,7 @@
         <v>46153</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45737</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45738</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45954</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45954</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45958</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>46150</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44866</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45370</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45370</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>44923</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45187</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45960</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45803</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44993</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45600</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45343</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>44497</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45337</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44818</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45723</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>44684</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45973</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45972</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45973</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45337</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45478</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45978</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45180</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45979</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>45307</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45197</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>44879</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45260</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45012</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45985</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45987</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45700</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45874</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45898</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45989</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45453</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45648</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45993</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44816</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45993</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45993</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45989</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45664</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45455</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45343</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45887</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45149</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45232</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46030</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45311</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>45072</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44579</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45573</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45144</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45586</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45526</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45709</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>44628</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45712</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45408</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46001</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45573</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45568</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>45398</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45846</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>46006</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>46007</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45054</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40790,7 +40790,7 @@
         <v>45194</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>46008</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45085</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44992</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>46169</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>45306</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45307</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45903</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
         <v>45493</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>45387</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>44463</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45803</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45474</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41739,7 +41739,7 @@
         <v>45189</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>45282</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45274</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45737</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>46031</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45265</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>46031</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>46035</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45763</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>45579</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45882</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45926</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>46036</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44893</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>46031</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>46041</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46041</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>44729</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45833</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>46043</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>46042</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>46042</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45938</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>46043</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>46043</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46043</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>46043</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>46035</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45336</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45420</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45079</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45120</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46048</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45307</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45002</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>45465</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45012</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46057</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44596,7 +44596,7 @@
         <v>46057</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>46177</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45228</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>45343</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45812</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         <v>46069</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>45042</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45672</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45338</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46181</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>46076</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45014</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45894</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45831</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>44988</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>46083</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45894</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45894</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45415</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>44998</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45019</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>45882</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45124</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>44497</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46188</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>44894</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45465</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45668</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>46055</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>45191</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45902</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45300</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>46092</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>45301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46092</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45470</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>46094</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>46041</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>46094</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45712</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>46095</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45098</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45608</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>44894</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45321</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46198</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45315</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45077</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>45077</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45566</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>44991</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>45022</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>46111</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45254</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>44963</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45356</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45727</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45267</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45394</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>46113</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>46120</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46120</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>46120</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>45180</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>46120</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45379</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45282</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>46202</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>45465</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>46244</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>45544</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>46129</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>45343</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50063,7 +50063,7 @@
         <v>45586</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>44923</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45414</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>45334</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45646</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45334</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45338</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>44972</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45303</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45015</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45461</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45476</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>45525</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>45716</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>46112</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45043</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46250</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>45197</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45474</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>46250</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45253</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>44767</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>44732</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>46253</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>44995</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>44596</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44992</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46253</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>46253</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>46253</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52371,7 +52371,7 @@
         <v>45165</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52449,7 +52449,7 @@
         <v>46212</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
         <v>46212</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>46212</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>46212</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45149</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45182</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>45247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45310</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45110</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>46256</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>44933</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53277,7 +53277,7 @@
         <v>46214</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>46255</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45685</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>46260</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45278</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>45278</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>45506</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>46218</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45119</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>45141</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>45141</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>44858</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54163,7 +54163,7 @@
         <v>46217</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54241,7 +54241,7 @@
         <v>46260</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54314,7 +54314,7 @@
         <v>46261</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>44468</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45738</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>46222</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>45090</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45121</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54762,7 +54762,7 @@
         <v>45738</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45738</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45566</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45357</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45622</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>46223</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45189</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45387</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>44991</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>44907</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55497,7 +55497,7 @@
         <v>45275</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45119</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>44694</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>44946</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45737</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>45776</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>46271</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>46273</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>46271</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>46271</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45443</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>46271</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>46272</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56544,7 +56544,7 @@
         <v>45574</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56617,7 +56617,7 @@
         <v>46135</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45414</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56763,7 +56763,7 @@
         <v>46276</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>46276</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56914,7 +56914,7 @@
         <v>46276</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56987,7 +56987,7 @@
         <v>46237</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>46276</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>46205</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>46190</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>44497</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>45357</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45370</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45603</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46276</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>46280</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45217</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45233</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45700</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45183</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45517</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45498</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>46272</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         <v>46189</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58306,7 +58306,7 @@
         <v>45533</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58379,7 +58379,7 @@
         <v>45797</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>45799</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58530,7 +58530,7 @@
         <v>45648</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>45800</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>45670</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>45553</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>45804</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45804</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45810</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>45396</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45810</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>44537</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45420</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>45843</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45737</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59479,7 +59479,7 @@
         <v>45831</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59552,7 +59552,7 @@
         <v>45706</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>45737</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59698,7 +59698,7 @@
         <v>45737</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>45833</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45832</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>45758</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59995,7 +59995,7 @@
         <v>45440</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60068,7 +60068,7 @@
         <v>45609</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>45321</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>45408</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>45736</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45014</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45736</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>45706</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45715</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>45845</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45818</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60798,7 +60798,7 @@
         <v>45749</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45860</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60944,7 +60944,7 @@
         <v>45827</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61017,7 +61017,7 @@
         <v>44712</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>45874</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61168,7 +61168,7 @@
         <v>45874</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45874</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61314,7 +61314,7 @@
         <v>44713</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>45607</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61470,7 +61470,7 @@
         <v>45607</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61548,7 +61548,7 @@
         <v>44607</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45546</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>45558</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61777,7 +61777,7 @@
         <v>45558</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61855,7 +61855,7 @@
         <v>45418</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45581</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>44501</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>45617</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>44970</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45089</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>44459</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>44713</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>44809</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45440</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45677</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45677</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45503</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>45659</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>44784</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>44841</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63038,7 +63038,7 @@
         <v>45012</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>44676</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63184,7 +63184,7 @@
         <v>44956</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45069</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63330,7 +63330,7 @@
         <v>45120</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45728</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63476,7 +63476,7 @@
         <v>45702</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45702</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63622,7 +63622,7 @@
         <v>45726</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63695,7 +63695,7 @@
         <v>45734</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63768,7 +63768,7 @@
         <v>45811</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>45811</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         <v>45811</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63987,7 +63987,7 @@
         <v>45901</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64060,7 +64060,7 @@
         <v>45945</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64133,7 +64133,7 @@
         <v>45946</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>46127</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         <v>46141</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>46148</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>46272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>44918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45267</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45303</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45020</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45940</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45952</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45000</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44700</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44970</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>46213</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44480</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44494</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45465</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45492</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45602</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44910</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45929</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>46091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44476</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45016</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45716</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>46013</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45315</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>45244</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45303</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44767</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45665</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45357</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45468</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45139</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45506</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45946</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45577</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44971</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45938</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44743</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>45738</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>46108</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46134</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45993</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45477</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45015</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45945</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46150</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45343</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45835</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45754</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45607</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45009</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46188</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45842</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45755</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45511</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44686</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46253</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45267</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45328</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45352</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45302</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44767</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>46287</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44767</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45128</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45607</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45748</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45477</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45446</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45274</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45295</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45467</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45547</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45574</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46058</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44705</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44533</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44536</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44670</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44558</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44744</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44560</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44767</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44628</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44592</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44623</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44837</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44627</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44888</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>44744</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44491</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44841</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44862</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44706</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44470</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44697</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44672</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45035</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44742</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45337</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45043</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45532</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45532</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45300</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45232</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44893</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45379</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45197</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>44847</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45336</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45416</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45420</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45533</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44487</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45144</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45144</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45323</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45586</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45465</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45470</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45419</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45498</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45282</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45797</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45533</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>46031</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45646</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46035</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45887</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45887</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46036</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46031</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44497</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45511</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45833</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45894</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46042</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46042</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45896</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45895</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>46041</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>46043</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>46043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>46043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>46035</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>46043</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45737</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45900</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45900</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45900</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45900</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45900</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45589</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45900</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45573</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44993</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45799</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44995</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45648</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46057</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>45792</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44938</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45915</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45408</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45553</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45804</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45800</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45120</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>46069</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45804</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45103</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44923</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45577</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45925</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45925</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45198</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45930</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44894</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45042</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>46083</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45894</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45338</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45894</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45396</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45810</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45882</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45931</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45894</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45583</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45933</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45915</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46092</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46092</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45939</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45939</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45544</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44946</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45939</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45939</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46095</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>46094</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>44744</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45228</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45568</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45945</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44988</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45525</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45398</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45945</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45945</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45107</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45343</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45586</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45953</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45954</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45954</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45712</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>46113</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45343</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44634</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45355</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45180</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45958</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45121</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45121</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45960</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45112</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45577</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>46120</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46120</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46120</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45307</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>46120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45600</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45803</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>44995</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45079</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45166</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45972</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45672</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45012</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>45973</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45077</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45077</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45144</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45119</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>44992</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45275</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45166</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45420</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>46129</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45978</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45979</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45465</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45014</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45777</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45357</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45668</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45482</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45987</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45749</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45989</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45015</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>44795</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44537</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>45989</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45187</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45693</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45993</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45993</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45455</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>44853</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45707</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46136</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45846</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45568</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>46001</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45709</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45544</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45461</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45412</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>46007</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45338</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45089</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44853</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45110</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45247</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45554</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45022</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45027</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45843</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45334</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45738</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45197</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46141</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>44468</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45083</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45474</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44918</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45012</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45054</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>44991</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45706</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45465</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45737</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45832</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45069</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45226</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45737</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>46147</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44846</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45098</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45737</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46149</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45831</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>46150</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>46153</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45119</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45260</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>45833</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45555</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45440</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45723</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45758</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46030</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>44579</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45493</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45342</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45453</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45738</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45738</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45887</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45311</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45307</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45761</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45582</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45366</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45446</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45874</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45898</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45716</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45566</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44894</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45321</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45408</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45715</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45736</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45014</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45845</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45706</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45736</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45609</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45727</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45749</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45818</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45343</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45903</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>46169</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45247</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45119</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45860</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45882</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45478</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45763</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45579</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45600</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45938</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45002</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45926</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45827</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45326</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>44712</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45544</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>44824</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45121</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45281</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44544</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45387</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45394</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45812</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45338</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45577</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45007</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45474</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45180</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45643</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45149</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45874</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45874</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45260</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45168</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>44587</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46188</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45278</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45902</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>44904</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45561</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>46055</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>46041</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45874</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45668</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45127</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45315</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45755</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45124</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45414</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>44596</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45729</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45712</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45586</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45586</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45159</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>46198</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45338</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>44627</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45573</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45049</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44713</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45418</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>45727</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>46202</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45546</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45581</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45607</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45119</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45558</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45558</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45555</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>44607</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45607</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45189</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46112</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45165</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46250</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45110</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45622</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>46250</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>46253</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46253</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45665</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46253</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45141</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45083</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>46212</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45090</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45665</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>46212</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>46214</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>46212</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46212</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>46255</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>44694</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45204</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45132</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>46260</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45415</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46217</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46260</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>46256</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>45700</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>44655</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>46261</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>46218</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45387</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45188</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>44729</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45119</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45244</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45278</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>44858</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>44816</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45173</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45300</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>46223</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45315</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45315</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>46222</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>45328</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>44817</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45338</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45343</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45343</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46271</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>46271</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>44855</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45474</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45356</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>46135</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46272</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>46272</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51736,7 +51736,7 @@
         <v>46273</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>44961</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51882,7 +51882,7 @@
         <v>44907</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51955,7 +51955,7 @@
         <v>44595</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>44497</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52101,7 +52101,7 @@
         <v>45267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>46205</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45282</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45301</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>46276</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52476,7 +52476,7 @@
         <v>46276</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52549,7 +52549,7 @@
         <v>46276</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45265</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>46276</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>46276</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45226</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>46237</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45405</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>46190</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>46280</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>44847</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45254</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45191</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45652</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>44513</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>46284</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53654,7 +53654,7 @@
         <v>45274</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>46287</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>46287</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45566</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>46288</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>44972</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46271</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>44601</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>46287</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>44998</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>46288</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46271</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45072</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>46189</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45198</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>45233</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         <v>45233</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>45331</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>45343</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>46244</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45476</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>46289</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55441,7 +55441,7 @@
         <v>44858</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>44572</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>44732</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>46290</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>44743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>44767</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45229</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>44879</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>44984</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>45253</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>44915</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45465</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45496</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45608</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45426</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45470</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>44876</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>44684</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>44628</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45755</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45664</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>44923</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57057,7 +57057,7 @@
         <v>45310</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57130,7 +57130,7 @@
         <v>44991</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>44645</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>45307</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45085</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45049</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45370</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>45370</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45357</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>45144</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45532</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45520</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>44945</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>44963</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>45526</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>45247</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58235,7 +58235,7 @@
         <v>45258</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>45116</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>45190</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>44984</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>45121</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45506</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45306</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>45182</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45019</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>44992</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>44933</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>45149</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>45002</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>45648</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59423,7 +59423,7 @@
         <v>45307</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59496,7 +59496,7 @@
         <v>45467</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59569,7 +59569,7 @@
         <v>44774</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>44866</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45334</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45685</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59861,7 +59861,7 @@
         <v>45737</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45477</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60007,7 +60007,7 @@
         <v>45737</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60080,7 +60080,7 @@
         <v>45738</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45000</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60226,7 +60226,7 @@
         <v>45644</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>45554</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45343</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60450,7 +60450,7 @@
         <v>45490</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45554</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60596,7 +60596,7 @@
         <v>45386</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>45134</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45106</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45194</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45544</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45377</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45364</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>45646</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45776</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45443</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>44497</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>45217</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45357</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>45233</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>45414</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61691,7 +61691,7 @@
         <v>45370</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61764,7 +61764,7 @@
         <v>45574</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45700</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61910,7 +61910,7 @@
         <v>45603</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>45183</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62056,7 +62056,7 @@
         <v>45517</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         <v>44713</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62202,7 +62202,7 @@
         <v>44676</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62275,7 +62275,7 @@
         <v>44501</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62348,7 +62348,7 @@
         <v>45617</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62421,7 +62421,7 @@
         <v>44970</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62499,7 +62499,7 @@
         <v>45089</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>44809</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45440</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45677</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45677</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45503</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>45659</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>44784</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>44841</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>45012</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63229,7 +63229,7 @@
         <v>44956</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>45069</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63375,7 +63375,7 @@
         <v>45120</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>45728</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45702</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63594,7 +63594,7 @@
         <v>45702</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63667,7 +63667,7 @@
         <v>45726</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45734</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63813,7 +63813,7 @@
         <v>45811</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45811</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>45811</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>45901</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64105,7 +64105,7 @@
         <v>45945</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>45946</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>46127</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64324,7 +64324,7 @@
         <v>46141</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64402,7 +64402,7 @@
         <v>46148</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>46272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>44918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45267</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45303</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45020</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45940</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45952</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45000</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44700</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44970</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>46213</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44480</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44494</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45465</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45492</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45602</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44910</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45929</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>46091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44476</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45016</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45716</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>46013</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45315</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>45244</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45303</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44767</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45665</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45357</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45468</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45139</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45506</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45946</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45577</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44971</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45938</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44743</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>45738</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>46108</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46134</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45993</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45477</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45015</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45945</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46150</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45343</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45835</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45754</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45607</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45009</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46188</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45842</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45755</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45511</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44686</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46253</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45267</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45328</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45352</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45302</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44767</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>46287</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44767</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45128</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45607</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45748</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45477</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45446</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45274</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45295</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45467</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45547</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45574</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46058</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44705</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44533</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44536</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44670</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44558</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44744</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44560</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44767</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44628</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44592</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44623</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44837</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44627</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44888</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>44744</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44491</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44841</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44862</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44706</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44470</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44697</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44672</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45035</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44742</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45337</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45043</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45532</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45532</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45300</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45232</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44893</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45379</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45197</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>44847</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45336</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45416</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45420</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45533</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44487</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45144</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45144</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45323</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45586</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45465</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45470</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45419</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45498</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45282</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45797</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45533</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>46031</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45646</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46035</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45887</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45887</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46036</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46031</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44497</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45511</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45833</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45894</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46042</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46042</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45896</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45895</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>46041</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>46043</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>46043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>46043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>46035</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>46043</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45737</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45900</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45900</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45900</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45900</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45900</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45589</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45900</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45573</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44993</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45799</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44995</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45648</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46057</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>45792</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44938</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45915</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45408</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45553</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45804</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45800</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45120</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>46069</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45804</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45103</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44923</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45577</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45925</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45925</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45198</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45930</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44894</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45042</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>46083</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45894</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45338</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45894</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45396</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45810</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45882</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45931</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45894</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45583</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45933</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45915</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46092</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46092</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45939</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45939</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45544</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44946</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45939</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45939</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46095</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>46094</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>44744</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45228</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45568</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45945</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44988</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45525</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45398</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45945</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45945</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45107</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45343</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45586</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45953</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45954</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45954</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45712</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>46113</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45343</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44634</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45355</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45180</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45958</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45121</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45121</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45960</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45112</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45577</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>46120</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46120</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46120</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45307</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>46120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45600</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45803</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>44995</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45079</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45166</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45972</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45672</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45012</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>45973</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45077</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45077</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45144</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45119</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>44992</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45275</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45166</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45420</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>46129</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45978</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45979</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45465</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45014</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45777</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45357</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45668</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45482</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45987</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45749</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45989</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45015</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>44795</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44537</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>45989</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45187</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45693</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45993</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45993</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45455</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>44853</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45707</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46136</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45846</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45568</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>46001</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45709</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45544</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45461</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45412</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>46007</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45338</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45089</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44853</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45110</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45247</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45554</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45022</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45027</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45843</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45334</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45738</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45197</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46141</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>44468</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45083</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45474</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44918</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45012</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45054</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>44991</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45706</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45465</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45737</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45832</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45069</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45226</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45737</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>46147</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44846</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45098</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45737</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46149</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45831</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>46150</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>46153</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45119</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45260</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>45833</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45555</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45440</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45723</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45758</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46030</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>44579</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45493</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45342</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45453</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45738</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45738</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45887</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45311</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45307</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45761</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45582</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45366</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45446</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45874</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45898</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45716</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45566</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44894</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45321</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45408</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45715</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45736</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45014</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45845</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45706</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45736</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45609</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45727</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45749</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45818</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45343</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45903</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>46169</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45247</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45119</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45860</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45882</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45478</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45763</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45579</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45600</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45938</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45002</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45926</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45827</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45326</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>44712</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45544</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>44824</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45121</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45281</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44544</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45387</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45394</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45812</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45338</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45577</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45007</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45474</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45180</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45643</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45149</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45874</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45874</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45260</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45168</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>44587</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46188</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45278</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45902</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>44904</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45561</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>46055</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>46041</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45874</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45668</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45127</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45315</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45755</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45124</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45414</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>44596</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45729</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45712</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45586</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45586</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45159</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>46198</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45338</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>44627</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45573</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45049</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44713</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45418</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>45727</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>46202</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45546</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45581</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45607</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45119</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45558</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45558</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45555</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>44607</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45607</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45189</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46112</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45165</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46250</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45110</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45622</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>46250</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>46253</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46253</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45665</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46253</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45141</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45083</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>46212</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45090</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45665</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>46212</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>46214</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>46212</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46212</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>46255</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>44694</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45204</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45132</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>46260</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45415</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46217</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46260</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>46256</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>45700</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>44655</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>46261</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>46218</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45387</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45188</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>44729</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45119</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45244</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45278</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>44858</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>44816</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45173</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45300</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>46223</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45315</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45315</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>46222</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>45328</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>44817</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45338</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45343</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45343</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46271</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>46271</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>44855</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45474</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45356</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>46135</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46272</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>46272</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51736,7 +51736,7 @@
         <v>46273</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>44961</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51882,7 +51882,7 @@
         <v>44907</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51955,7 +51955,7 @@
         <v>44595</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>44497</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52101,7 +52101,7 @@
         <v>45267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>46205</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45282</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45301</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>46276</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52476,7 +52476,7 @@
         <v>46276</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52549,7 +52549,7 @@
         <v>46276</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45265</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>46276</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>46276</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45226</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>46237</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45405</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>46190</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>46280</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>44847</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45254</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45191</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45652</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>44513</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>46284</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53654,7 +53654,7 @@
         <v>45274</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>46287</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>46287</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45566</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>46288</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>44972</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46271</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>44601</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>46287</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>44998</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>46288</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46271</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45072</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>46189</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45198</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>45233</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         <v>45233</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>45331</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>45343</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>46244</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45476</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>46289</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55441,7 +55441,7 @@
         <v>44858</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>44572</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>44732</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>46290</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>44743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>44767</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45229</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>44879</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>44984</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>45253</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>44915</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45465</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45496</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45608</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45426</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45470</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>44876</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>44684</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>44628</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45755</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45664</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>44923</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57057,7 +57057,7 @@
         <v>45310</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57130,7 +57130,7 @@
         <v>44991</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>44645</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>45307</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45085</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45049</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45370</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>45370</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45357</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>45144</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45532</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45520</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>44945</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>44963</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>45526</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>45247</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58235,7 +58235,7 @@
         <v>45258</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>45116</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>45190</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>44984</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>45121</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45506</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45306</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>45182</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45019</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>44992</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>44933</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>45149</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>45002</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>45648</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59423,7 +59423,7 @@
         <v>45307</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59496,7 +59496,7 @@
         <v>45467</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59569,7 +59569,7 @@
         <v>44774</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>44866</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45334</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45685</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59861,7 +59861,7 @@
         <v>45737</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45477</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60007,7 +60007,7 @@
         <v>45737</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60080,7 +60080,7 @@
         <v>45738</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45000</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60226,7 +60226,7 @@
         <v>45644</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>45554</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45343</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60450,7 +60450,7 @@
         <v>45490</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45554</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60596,7 +60596,7 @@
         <v>45386</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>45134</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45106</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45194</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45544</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45377</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45364</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>45646</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45776</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45443</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>44497</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>45217</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45357</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>45233</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>45414</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61691,7 +61691,7 @@
         <v>45370</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61764,7 +61764,7 @@
         <v>45574</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45700</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61910,7 +61910,7 @@
         <v>45603</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>45183</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62056,7 +62056,7 @@
         <v>45517</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         <v>44713</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62202,7 +62202,7 @@
         <v>44676</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62275,7 +62275,7 @@
         <v>44501</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62348,7 +62348,7 @@
         <v>45617</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62421,7 +62421,7 @@
         <v>44970</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62499,7 +62499,7 @@
         <v>45089</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>44809</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45440</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45677</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45677</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45503</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>45659</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>44784</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>44841</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>45012</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63229,7 +63229,7 @@
         <v>44956</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>45069</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63375,7 +63375,7 @@
         <v>45120</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>45728</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45702</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63594,7 +63594,7 @@
         <v>45702</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63667,7 +63667,7 @@
         <v>45726</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45734</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63813,7 +63813,7 @@
         <v>45811</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45811</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>45811</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>45901</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64105,7 +64105,7 @@
         <v>45945</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>45946</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>46127</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64324,7 +64324,7 @@
         <v>46141</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64402,7 +64402,7 @@
         <v>46148</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45925</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46136</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45940</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45930</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45952</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45671</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44970</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>46213</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44480</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44494</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45665</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45602</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45492</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>46091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45465</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45315</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45016</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45622</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44910</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44767</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45577</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44743</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45738</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44686</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45946</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44767</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45812</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45958</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45958</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>46108</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45993</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>46134</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45835</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45607</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45754</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45748</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45328</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44767</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>46150</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45009</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45352</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45128</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45511</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45267</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45343</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>46189</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>46188</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45842</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45546</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45607</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45302</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44971</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45468</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45477</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>46287</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46253</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44825</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45015</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45506</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45446</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45274</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45295</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45467</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45547</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45574</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46058</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44705</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44533</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44536</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44670</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44725</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44560</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44672</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44558</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44767</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44744</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44609</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44628</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44572</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44607</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44623</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44623</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44837</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44627</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44888</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44744</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>44491</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44841</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44862</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44866</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44706</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44767</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44838</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44713</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>44522</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44518</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44587</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44697</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44645</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44672</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45416</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45338</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45520</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45112</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45643</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45474</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45121</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45144</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44645</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45665</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44824</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45127</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45577</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44744</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45419</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45554</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45544</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45342</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45307</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44497</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45357</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45370</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45603</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45132</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44846</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45110</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46001</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45217</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45887</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45887</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45568</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45652</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45233</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45846</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45761</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46006</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>44634</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45665</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>46007</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44961</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45586</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45693</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45465</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44655</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45405</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45889</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45803</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45707</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45183</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45343</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46031</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45896</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45517</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45089</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46031</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45900</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45900</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45173</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45900</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45544</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46035</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45900</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45900</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45357</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45116</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45555</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>46031</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45204</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>46041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>46041</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45900</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45737</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45833</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45233</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45233</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45582</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>46043</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45260</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46043</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46043</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45498</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45555</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46043</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46035</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45533</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45797</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45792</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45915</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44487</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45799</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>44938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45648</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45800</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45343</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45343</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45670</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45600</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45121</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45121</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>45544</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45925</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45532</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45925</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45925</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>46057</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45930</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45931</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45244</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44627</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45586</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45229</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45326</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45933</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46069</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45915</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45496</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45119</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45939</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44513</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45939</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44984</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45939</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45939</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45561</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45532</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45532</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45338</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45577</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44572</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45000</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45945</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45323</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45568</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44742</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45945</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45945</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45396</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45446</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45810</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>46076</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44945</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45894</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45831</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>45477</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>46083</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45894</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45894</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>45953</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45882</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45727</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>45954</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45954</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45958</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45085</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45960</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>46092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45803</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44817</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>46092</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44587</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45069</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46094</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45364</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>46095</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45973</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45972</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45973</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>44774</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45247</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45485</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44537</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45978</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45979</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45420</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45121</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45583</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46111</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45985</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44847</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45281</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>45987</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45554</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46113</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46120</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45989</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>46120</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>46120</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>46120</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45993</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45993</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45993</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45989</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45226</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45843</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>45668</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46129</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>44855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45737</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45706</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45737</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45166</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45166</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45737</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45258</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>44595</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45470</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45027</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45833</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45832</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45144</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45144</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45331</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45338</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45338</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45755</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45083</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45758</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45440</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45035</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45644</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45159</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45461</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45355</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>45083</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45198</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>44544</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>45511</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>46136</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45609</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45321</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45589</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>45408</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45736</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45014</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45577</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45736</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45706</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>44853</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45845</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45554</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45533</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>44853</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45777</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45818</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45729</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45197</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45749</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45749</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45103</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45190</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>44984</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44858</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45226</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44599</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45134</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>44876</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44915</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45482</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45366</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45315</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45467</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45247</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44995</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45860</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>44795</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45002</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45755</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46141</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45328</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>44904</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45827</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>44847</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>44712</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45426</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44918</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45412</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>45049</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45386</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>46147</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45377</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45737</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45738</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>46149</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44866</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45370</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45370</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>44923</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>46153</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45187</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46150</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44993</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45600</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45343</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45723</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>44497</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45337</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>44818</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44684</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45874</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45898</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45453</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45874</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45887</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>46030</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45337</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44579</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45874</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45874</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45478</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45180</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45307</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45197</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>44879</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45260</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45012</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>44713</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45607</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45607</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>44607</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>46169</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>45903</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45546</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45558</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45558</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45418</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45700</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45581</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46365,7 +46365,7 @@
         <v>45763</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45579</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45882</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45926</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45938</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45648</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>44816</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>45664</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>45455</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45343</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>45149</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47173,7 +47173,7 @@
         <v>45232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45646</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45311</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45072</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45573</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46177</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45144</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45586</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45812</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45526</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46181</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45709</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>44628</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45712</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
         <v>46188</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45408</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45573</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45668</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46055</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>45902</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         <v>45398</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>46041</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45712</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45054</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>45194</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>45085</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>44992</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>46198</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45306</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45307</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45493</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45387</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45474</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>45189</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46202</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45282</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>45274</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45737</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45265</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46112</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>44893</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>44729</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>46212</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46212</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>46212</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>46212</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46256</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46214</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>45336</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45420</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45079</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45315</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45120</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45307</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45002</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46260</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46218</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45465</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46217</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>46260</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>46261</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45012</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>46222</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45228</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>46223</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45343</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>45042</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45672</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>45338</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>46273</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>46271</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46271</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45014</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46272</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>44988</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45415</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>44998</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45019</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46135</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>45124</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44497</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>46276</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46276</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46276</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46237</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>46276</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>46205</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>46276</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>46280</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>44894</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45465</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45191</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45300</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45301</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45470</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45098</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45608</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>44894</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45321</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>45315</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46271</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45077</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45077</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45566</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>44991</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45022</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>46284</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>46287</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45254</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>46244</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>44963</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46189</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>46271</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45356</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45727</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45267</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45394</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46287</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>46288</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>46288</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46272</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45180</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45379</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56360,7 +56360,7 @@
         <v>45282</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>46287</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45465</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
         <v>46250</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45544</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56735,7 +56735,7 @@
         <v>45119</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>45343</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>46289</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56959,7 +56959,7 @@
         <v>46290</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>46250</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45586</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>44923</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45414</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45334</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45646</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45334</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>44972</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45303</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>46272</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>45476</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>45015</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45525</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45716</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>46296</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45043</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>45197</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>46190</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>46253</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45474</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>46295</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58585,7 +58585,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46253</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>46255</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58892,7 +58892,7 @@
         <v>45253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         <v>44767</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>44732</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>44995</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59184,7 +59184,7 @@
         <v>45106</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>44596</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>44992</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>45165</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59481,7 +59481,7 @@
         <v>45149</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>45182</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>45247</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45310</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45110</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>44933</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45685</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>45278</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45278</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45506</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45119</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45141</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45141</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>44858</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45738</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45090</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>45121</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45738</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>45738</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>45566</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45357</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>45622</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>45189</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>45387</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61248,7 +61248,7 @@
         <v>44991</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>44907</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>45275</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45119</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>44694</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>44946</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61691,7 +61691,7 @@
         <v>45737</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61764,7 +61764,7 @@
         <v>45776</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45443</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61910,7 +61910,7 @@
         <v>45574</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>45414</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62056,7 +62056,7 @@
         <v>44501</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         <v>45617</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62202,7 +62202,7 @@
         <v>44970</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62280,7 +62280,7 @@
         <v>45089</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>44713</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>44809</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62499,7 +62499,7 @@
         <v>45440</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>45677</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45677</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45503</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45659</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>44784</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>44841</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>45012</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>44676</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>44956</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63229,7 +63229,7 @@
         <v>45069</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>45120</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63375,7 +63375,7 @@
         <v>45728</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>45702</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45702</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63594,7 +63594,7 @@
         <v>45726</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63667,7 +63667,7 @@
         <v>45734</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45811</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63813,7 +63813,7 @@
         <v>45811</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45811</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>45901</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>45945</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64105,7 +64105,7 @@
         <v>45946</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>46127</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>46141</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>46148</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45925</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46136</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45940</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45930</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45952</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45671</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44970</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>46213</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44480</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44494</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45665</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45602</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45492</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>46091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45465</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45315</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45016</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45622</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44910</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44767</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45577</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44743</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45738</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44686</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45946</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44767</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45812</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45958</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45958</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>46108</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45993</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>46134</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45835</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45607</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45754</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45748</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45328</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44767</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>46150</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45009</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45352</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45128</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45511</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45267</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45343</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>46189</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>46188</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45842</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45546</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45607</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45302</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44971</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45468</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45477</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>46287</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46253</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44825</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45015</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45506</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45446</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45274</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45295</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45467</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45547</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45574</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46058</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44705</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>44533</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44536</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44670</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44725</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44560</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44672</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44558</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44767</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44744</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44609</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44628</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44572</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44607</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44623</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44623</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44837</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44627</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44888</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44744</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>44491</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44841</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44862</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44866</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44706</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44767</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44838</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44713</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>44522</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44518</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44587</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44697</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44645</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44672</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45416</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45338</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45520</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45112</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45643</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45474</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45121</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45144</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44645</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45665</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44824</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45127</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45577</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44744</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45419</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45554</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45544</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45342</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45307</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44497</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45357</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45370</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45603</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45132</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44846</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45110</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46001</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45217</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45887</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45887</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45568</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45652</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45233</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45846</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45761</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46006</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>44634</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45665</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>46007</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44961</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45586</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45693</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45465</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44655</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45405</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45889</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45803</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45707</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45183</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45343</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46031</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45896</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45517</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45089</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46031</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45900</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45900</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45173</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45900</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45544</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46035</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45900</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45900</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45357</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45116</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45555</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>46031</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45204</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>46041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>46041</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45900</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45737</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45833</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45233</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45233</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45582</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>46043</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45260</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46043</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46043</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45498</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45555</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46043</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46035</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45533</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45797</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45792</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45915</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44487</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45799</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>44938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45648</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45800</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45343</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45343</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45670</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45600</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45121</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45121</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>45544</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45925</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45532</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45925</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45925</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>46057</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45930</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45931</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45244</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44627</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45586</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45229</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45326</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45933</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46069</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45915</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45496</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45119</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45939</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44513</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45939</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44984</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45939</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45939</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45561</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45532</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45532</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45338</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45577</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44572</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45000</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45945</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45323</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45568</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44742</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45945</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45945</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45396</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45446</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45810</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>46076</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44945</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45894</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45831</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>45477</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>46083</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45894</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45894</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>45953</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45882</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45727</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>45954</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45954</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45958</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45085</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45960</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>46092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45803</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44817</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>46092</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44587</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45069</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46094</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45364</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>46095</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45973</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45972</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45973</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>44774</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45247</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45485</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44537</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45978</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45979</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45420</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45121</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45583</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46111</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45985</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44847</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45281</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>45987</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45554</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46113</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46120</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45989</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>46120</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>46120</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>46120</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45993</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45993</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45993</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45989</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45226</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45843</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>45668</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46129</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>44855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45737</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45706</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45737</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45166</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45166</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45737</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45258</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>44595</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45470</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45027</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45833</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45832</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45144</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45144</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45331</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45338</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45338</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45755</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45083</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45758</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45440</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45035</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45644</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45159</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45461</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45355</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>45083</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45198</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>44544</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>45511</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>46136</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45609</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45321</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45589</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>45408</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45736</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45014</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45577</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45736</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45706</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>44853</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45845</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45554</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45533</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>44853</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45777</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45818</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45729</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45197</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45749</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45749</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45103</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45190</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>44984</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44858</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45226</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44599</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45134</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>44876</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44915</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45482</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45366</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45315</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45467</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45247</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44995</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45860</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>44795</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45002</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45755</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46141</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45328</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>44904</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45827</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>44847</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>44712</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45426</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44918</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45412</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>45049</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45386</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>46147</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45377</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45737</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45738</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>46149</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44866</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45370</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45370</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>44923</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>46153</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45187</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46150</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44993</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45600</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45343</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45723</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>44497</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45337</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>44818</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44684</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45874</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45898</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45453</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45874</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45887</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>46030</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45337</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44579</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45874</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45874</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45478</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45180</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45307</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45197</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>44879</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45260</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45012</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>44713</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45607</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45607</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>44607</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>46169</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>45903</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45546</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45558</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45558</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45418</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45700</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45581</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46365,7 +46365,7 @@
         <v>45763</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45579</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45882</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45926</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45938</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45648</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>44816</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>45664</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>45455</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45343</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>45149</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47173,7 +47173,7 @@
         <v>45232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45646</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45311</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45072</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45573</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46177</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45144</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45586</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45812</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45526</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46181</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45709</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>44628</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45712</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
         <v>46188</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45408</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45573</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45668</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46055</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>45902</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         <v>45398</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>46041</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45712</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45054</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>45194</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>45085</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>44992</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>46198</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45306</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45307</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45493</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45387</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45474</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>45189</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46202</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45282</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>45274</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45737</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45265</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46112</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>44893</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>44729</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>46212</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46212</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>46212</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>46212</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46256</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46214</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>45336</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45420</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45079</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45315</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45120</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45307</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45002</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46260</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46218</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45465</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46217</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>46260</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>46261</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45012</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>46222</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45228</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>46223</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45343</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>45042</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45672</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>45338</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>46273</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>46271</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46271</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45014</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46272</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>44988</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45415</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>44998</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45019</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46135</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>45124</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44497</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>46276</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46276</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46276</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46237</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>46276</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>46205</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>46276</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>46280</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>44894</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45465</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45191</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45300</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45301</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45470</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45098</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45608</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>44894</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45321</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>45315</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46271</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45077</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45077</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45566</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>44991</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45022</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>46284</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>46287</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45254</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>46244</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>44963</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46189</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>46271</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45356</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45727</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45267</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45394</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46287</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>46288</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>46288</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46272</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45180</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45379</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56360,7 +56360,7 @@
         <v>45282</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>46287</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45465</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
         <v>46250</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45544</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56735,7 +56735,7 @@
         <v>45119</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>45343</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>46289</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56959,7 +56959,7 @@
         <v>46290</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>46250</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45586</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>44923</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45414</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45334</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45646</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45334</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>44972</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45303</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>46272</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>45476</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>45015</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45525</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45716</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>46296</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45043</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>45197</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>46190</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>46253</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45474</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>46295</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58585,7 +58585,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46253</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>46255</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58892,7 +58892,7 @@
         <v>45253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         <v>44767</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>44732</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>44995</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59184,7 +59184,7 @@
         <v>45106</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>44596</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>44992</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>45165</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59481,7 +59481,7 @@
         <v>45149</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>45182</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>45247</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45310</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45110</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>44933</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45685</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>45278</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45278</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45506</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45119</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45141</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45141</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>44858</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45738</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45090</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>45121</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45738</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>45738</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>45566</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45357</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>45622</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>45189</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>45387</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61248,7 +61248,7 @@
         <v>44991</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>44907</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>45275</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45119</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>44694</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>44946</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61691,7 +61691,7 @@
         <v>45737</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61764,7 +61764,7 @@
         <v>45776</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45443</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61910,7 +61910,7 @@
         <v>45574</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>45414</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62056,7 +62056,7 @@
         <v>44501</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         <v>45617</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62202,7 +62202,7 @@
         <v>44970</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62280,7 +62280,7 @@
         <v>45089</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>44713</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>44809</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62499,7 +62499,7 @@
         <v>45440</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>45677</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45677</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45503</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45659</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>44784</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>44841</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>45012</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>44676</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>44956</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63229,7 +63229,7 @@
         <v>45069</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>45120</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63375,7 +63375,7 @@
         <v>45728</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>45702</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45702</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63594,7 +63594,7 @@
         <v>45726</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63667,7 +63667,7 @@
         <v>45734</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45811</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63813,7 +63813,7 @@
         <v>45811</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45811</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>45901</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>45945</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64105,7 +64105,7 @@
         <v>45946</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>46127</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>46141</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>46148</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45357</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>44918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45267</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45755</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46157</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45000</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44700</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>45671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44970</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>46213</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44480</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44494</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45727</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45303</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45465</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44767</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45492</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45665</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44910</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45929</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45315</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45016</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>46091</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45244</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>46013</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>46304</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>46091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45128</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45357</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45343</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45093</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45139</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45265</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45506</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>45477</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45009</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45558</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>45755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45577</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45930</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44686</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44971</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45738</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45938</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45812</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44825</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45958</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45958</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45835</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45754</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45267</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45328</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45352</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45302</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45477</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44767</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45985</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45015</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>46108</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45993</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45112</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44767</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45833</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45946</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45845</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46188</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45842</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>46189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>46287</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>46279</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>46253</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>46058</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44536</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44670</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44705</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44558</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44744</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44725</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44560</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44767</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44609</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44572</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44627</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44491</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44596</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44838</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44713</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44706</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44522</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44518</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44685</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44767</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>44749</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44862</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44645</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44697</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44628</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45232</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44846</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45307</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45085</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>44893</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45379</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45049</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45098</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44672</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45336</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45370</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45370</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45416</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45035</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>44847</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45357</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45119</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45144</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45260</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45532</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45520</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45197</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45197</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45555</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44742</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44945</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44963</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45526</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45493</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45247</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45342</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45738</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45738</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45337</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45258</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44846</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45311</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45116</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45307</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45420</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45761</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45582</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45366</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45190</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45446</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44984</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45716</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45566</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45532</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45532</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45300</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44894</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45189</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45121</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45506</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45533</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45727</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44487</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45121</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45144</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45144</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45306</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45182</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45343</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45019</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>44992</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45323</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45586</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45197</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45465</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45149</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45002</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45470</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45648</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45307</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45467</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45247</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>44818</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45119</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45419</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44774</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45646</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>44866</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45334</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45098</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45478</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45887</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45887</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45600</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45887</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45685</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45737</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45889</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45477</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45282</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45737</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45738</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45326</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45000</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45894</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45896</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45895</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45895</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45898</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45644</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45554</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45343</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45485</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45900</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45490</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45554</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45900</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45386</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45134</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45106</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45900</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45900</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45337</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44497</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45511</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45544</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45194</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44824</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45544</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45121</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45377</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45900</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45281</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>44544</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45387</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45303</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45737</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45394</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45364</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45338</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45577</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45007</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>45646</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45737</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45474</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45776</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45589</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45792</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45643</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45149</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45573</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44993</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45915</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45260</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45168</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44587</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45443</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44497</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45217</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45357</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>44995</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45233</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45414</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45370</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45278</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>44938</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44904</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45561</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45408</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>44599</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45127</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45700</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45120</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45315</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45603</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45755</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45124</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45103</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45414</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45729</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44923</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45925</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45925</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45517</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45577</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45930</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45042</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45586</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45586</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45498</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45159</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45338</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45338</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44627</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45573</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45583</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45049</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45797</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45931</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45533</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45727</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45933</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45119</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45555</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45670</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45189</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45915</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45799</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45648</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>44946</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45165</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>45553</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45804</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>45800</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>44744</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45228</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45804</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44988</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45110</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45085</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45525</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45622</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45398</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45396</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45810</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45810</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45939</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45939</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45939</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45939</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45939</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45343</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45586</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45568</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45665</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45945</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45945</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45945</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45712</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45141</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45141</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45343</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>44634</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45355</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45420</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45180</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45083</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>44537</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45121</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45121</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45090</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45665</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45112</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45577</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45307</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45843</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>44694</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45204</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45600</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45415</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44995</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45706</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45737</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45832</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45700</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45079</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45166</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45737</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45737</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45672</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45953</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45954</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45954</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45012</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45958</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45960</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45077</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45077</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>45144</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44655</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45119</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44992</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45275</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45833</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45166</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45440</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45387</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45758</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45803</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45188</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44729</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45119</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>45465</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45244</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45278</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>44858</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45357</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45972</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>45321</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45408</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45668</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45715</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45736</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>44816</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45014</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45845</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45173</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45706</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45736</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45300</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45609</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>44795</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45973</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45973</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45749</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45315</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45818</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45187</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45693</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45455</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45328</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45860</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45707</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>44817</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45338</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45343</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45343</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45827</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>44712</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45709</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45544</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45978</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45874</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45874</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45979</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>44855</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45474</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45356</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>45089</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45874</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>44961</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44907</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>44595</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44497</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45267</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45110</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45282</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45301</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44713</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45418</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45247</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45546</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45581</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45607</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45554</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>45558</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45558</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44607</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45607</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>46095</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>46094</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47455,7 +47455,7 @@
         <v>45265</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45022</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>45027</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>45226</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45334</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45405</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47893,7 +47893,7 @@
         <v>45738</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45985</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>44847</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45197</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45191</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45652</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45083</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45474</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>44918</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45012</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45054</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>44991</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46111</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>44513</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45465</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45987</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>45989</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45989</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>45069</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49373,7 +49373,7 @@
         <v>45226</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45274</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>46120</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>46120</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46120</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45993</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45993</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>46120</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45993</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45846</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45568</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>46129</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>46001</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45566</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>44972</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>44601</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>44998</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45777</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>45072</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45482</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>46008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>46007</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45198</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45749</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45233</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45233</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45331</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>45343</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45476</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>44858</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>44572</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>44732</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45803</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>44743</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>44767</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>44853</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>45229</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>44879</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46136</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>44984</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>45253</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>44915</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>46031</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45461</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45465</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>45412</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45496</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>46035</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45608</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>45338</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53083,7 +53083,7 @@
         <v>45426</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>46036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
         <v>46031</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45470</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>44876</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>46042</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>46042</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53594,7 +53594,7 @@
         <v>44853</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>44684</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>44628</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46041</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>46041</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>46043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46043</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>46043</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>46035</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45755</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>46043</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>46043</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45664</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>46048</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>44923</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>45310</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>44991</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>44645</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46141</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>46057</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55069,7 +55069,7 @@
         <v>46147</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>46069</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>46149</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55288,7 +55288,7 @@
         <v>46150</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>46153</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>46076</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55517,7 +55517,7 @@
         <v>46083</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55590,7 +55590,7 @@
         <v>45894</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45894</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45882</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>45831</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45894</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45723</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46030</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>44579</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45453</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>46092</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>45887</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>46092</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>46094</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45874</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45898</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>45903</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>46169</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>45882</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56914,7 +56914,7 @@
         <v>45763</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56987,7 +56987,7 @@
         <v>45579</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>45938</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45926</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>46177</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45812</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>46181</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>46188</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45902</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46055</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>46041</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45668</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45712</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>46198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57936,7 +57936,7 @@
         <v>46202</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>46112</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>46212</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>46212</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46214</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46212</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>46212</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>46217</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>46218</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>46223</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>46222</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46271</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>46271</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>46135</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46272</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46273</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>46205</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59227,7 +59227,7 @@
         <v>46276</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>46276</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>46276</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59451,7 +59451,7 @@
         <v>46276</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59529,7 +59529,7 @@
         <v>46276</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>46237</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59675,7 +59675,7 @@
         <v>46280</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>46284</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59826,7 +59826,7 @@
         <v>46287</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>46287</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>46271</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>46287</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>46287</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>46288</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46272</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46271</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46189</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46244</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>46290</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>46250</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>46289</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>46250</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>46272</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>46253</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46295</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>46296</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46253</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46253</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>46253</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>46006</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45015</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>46256</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>46300</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46300</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46300</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46300</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>46300</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62003,7 +62003,7 @@
         <v>46255</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>46190</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>46260</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62222,7 +62222,7 @@
         <v>46260</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>46261</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>44713</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>44676</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>44501</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62587,7 +62587,7 @@
         <v>45617</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62660,7 +62660,7 @@
         <v>44970</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>45089</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44809</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>45440</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45677</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63030,7 +63030,7 @@
         <v>45677</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>45503</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45659</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>44784</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>44841</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>45012</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>44956</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>45069</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63614,7 +63614,7 @@
         <v>45120</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63687,7 +63687,7 @@
         <v>45728</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63760,7 +63760,7 @@
         <v>45702</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
         <v>45702</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45726</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63979,7 +63979,7 @@
         <v>45734</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64052,7 +64052,7 @@
         <v>45811</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>45811</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64198,7 +64198,7 @@
         <v>45811</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>45901</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>45945</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64417,7 +64417,7 @@
         <v>45946</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64490,7 +64490,7 @@
         <v>46127</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64563,7 +64563,7 @@
         <v>46141</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45357</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>44918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45267</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45755</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46157</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45000</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44700</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>45671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44970</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>46213</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44480</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44494</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45727</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45303</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45465</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44767</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45492</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45665</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44910</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45929</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45315</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45016</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>46091</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45244</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>46013</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>46304</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>46091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45128</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45357</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45343</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45093</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45139</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45265</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45506</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>45477</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45009</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45558</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>45755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45577</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45930</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44686</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44971</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45738</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45938</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45812</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44825</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45958</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45958</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45835</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45754</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45267</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45328</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45352</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45302</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45477</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44767</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45985</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45015</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>46108</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45993</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45112</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44767</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45833</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45946</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45845</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46188</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45842</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>46189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>46287</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>46279</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>46253</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>46058</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44536</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44670</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44705</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44558</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44744</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44725</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44560</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44767</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44609</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44572</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44627</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44491</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44596</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44838</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44713</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44706</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44522</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44518</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44685</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44767</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>44749</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44862</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44645</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44697</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44628</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45232</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44846</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45307</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45085</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>44893</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45379</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45049</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45098</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44672</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45336</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45370</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45370</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45416</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45035</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>44847</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45357</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45119</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45144</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45260</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45532</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45520</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45197</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45197</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45555</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44742</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44945</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44963</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45526</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45493</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45247</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45342</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45738</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45738</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45337</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45258</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44846</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45311</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45116</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45307</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45420</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45761</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45582</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45366</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45190</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45446</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44984</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45716</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45566</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45532</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45532</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45300</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44894</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45189</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45121</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45506</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45533</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45727</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44487</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45121</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45144</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45144</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45306</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45182</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45343</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45019</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>44992</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45323</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45586</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45197</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45465</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45149</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45002</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45470</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45648</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45307</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45467</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45247</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>44818</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45119</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45419</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44774</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45646</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>44866</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45334</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45098</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45478</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45887</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45887</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45600</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45887</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45685</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45737</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45889</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45477</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45282</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45737</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45738</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45326</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45000</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45894</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45896</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45895</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45895</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45898</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45644</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45554</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45343</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45485</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45900</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45490</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45554</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45900</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45386</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45134</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45106</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45900</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45900</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45337</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44497</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45511</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45544</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45194</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44824</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45544</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45121</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45377</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45900</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45281</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>44544</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45387</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45303</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45737</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45394</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45364</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45338</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45577</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45007</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>45646</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45737</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45474</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45776</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45589</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45792</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45643</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45149</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45573</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44993</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45915</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45260</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45168</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44587</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45443</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44497</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45217</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45357</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>44995</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45233</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45414</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45370</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45278</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>44938</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44904</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45561</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45408</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>44599</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45127</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45700</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45120</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45315</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45603</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45755</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45124</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45103</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45414</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45729</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44923</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45925</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45925</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45517</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45577</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45930</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45042</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45586</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45586</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45498</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45159</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45338</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45338</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44627</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45573</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45583</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45049</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45797</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45931</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45533</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45727</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45933</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45119</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45555</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45670</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45189</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45915</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45799</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45648</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>44946</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45165</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>45553</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45804</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>45800</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>44744</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45228</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45804</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44988</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45110</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45085</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45525</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45622</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45398</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45396</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45810</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45810</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45939</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45939</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45939</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45939</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45939</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45343</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45586</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45568</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45665</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45945</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45945</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45945</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45712</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45141</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45141</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45343</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>44634</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45355</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45420</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45180</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45083</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>44537</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45121</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45121</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45090</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45665</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45112</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45577</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45307</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45843</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>44694</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45204</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45600</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45415</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44995</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45706</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45737</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45832</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45700</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45079</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45166</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45737</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45737</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45672</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45953</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45954</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45954</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45012</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45958</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45960</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45077</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45077</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>45144</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44655</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45119</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44992</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45275</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45833</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45166</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45440</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45387</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45758</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45803</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45188</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44729</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45119</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>45465</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45244</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45278</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>44858</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45357</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45972</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>45321</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45408</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45668</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45715</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45736</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>44816</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45014</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45845</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45173</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45706</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45736</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45300</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45609</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>44795</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45973</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45973</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45749</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45315</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45818</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45187</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44246,7 +44246,7 @@
         <v>45693</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45455</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45328</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45860</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45707</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>44817</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45338</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45343</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45343</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45827</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>44712</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45709</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45544</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45978</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45874</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45874</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45979</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>44855</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45474</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45356</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>45089</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45874</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>44961</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44907</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>44595</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44497</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45267</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45110</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45282</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45301</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44713</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45418</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45247</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45546</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45581</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45607</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45554</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>45558</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45558</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44607</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45607</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>46095</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>46094</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47455,7 +47455,7 @@
         <v>45265</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45022</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>45027</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>45226</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45334</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45405</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47893,7 +47893,7 @@
         <v>45738</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45985</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>44847</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45197</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45191</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45652</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45083</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45474</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>44918</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45012</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45054</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>44991</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46111</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>44513</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45465</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45987</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>45989</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45989</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>45069</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49373,7 +49373,7 @@
         <v>45226</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45274</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>46120</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>46120</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46120</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45993</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45993</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>46120</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45993</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45846</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45568</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>46129</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>46001</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45566</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>44972</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>44601</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>44998</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45777</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>45072</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45482</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>46008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>46007</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45198</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45749</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45233</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45233</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45331</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>45343</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45476</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>44858</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>44572</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>44732</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45803</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>44743</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>44767</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>44853</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>45229</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>44879</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46136</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>44984</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>45253</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>44915</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>46031</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45461</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45465</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>45412</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45496</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>46035</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45608</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>45338</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53083,7 +53083,7 @@
         <v>45426</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>46036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
         <v>46031</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45470</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>44876</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>46042</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>46042</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53594,7 +53594,7 @@
         <v>44853</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>44684</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>44628</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46041</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>46041</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>46043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46043</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>46043</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>46035</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45755</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>46043</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>46043</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45664</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>46048</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>44923</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>45310</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>44991</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>44645</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46141</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>46057</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55069,7 +55069,7 @@
         <v>46147</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>46069</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>46149</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55288,7 +55288,7 @@
         <v>46150</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>46153</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>46076</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55517,7 +55517,7 @@
         <v>46083</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55590,7 +55590,7 @@
         <v>45894</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45894</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45882</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>45831</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45894</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45723</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46030</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>44579</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45453</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>46092</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>45887</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>46092</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>46094</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45874</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45898</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>45903</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>46169</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>45882</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56914,7 +56914,7 @@
         <v>45763</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56987,7 +56987,7 @@
         <v>45579</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>45938</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45926</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>46177</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45812</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>46181</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>46188</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45902</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46055</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>46041</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45668</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45712</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>46198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57936,7 +57936,7 @@
         <v>46202</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>46112</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>46212</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>46212</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46214</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46212</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>46212</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>46217</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>46218</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>46223</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>46222</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46271</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>46271</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>46135</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46272</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46273</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>46205</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59227,7 +59227,7 @@
         <v>46276</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>46276</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>46276</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59451,7 +59451,7 @@
         <v>46276</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59529,7 +59529,7 @@
         <v>46276</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>46237</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59675,7 +59675,7 @@
         <v>46280</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>46284</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59826,7 +59826,7 @@
         <v>46287</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>46287</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>46271</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>46287</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>46287</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>46288</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46272</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46271</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46189</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46244</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>46290</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>46250</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>46289</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>46250</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>46272</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>46253</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46295</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>46296</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46253</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46253</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>46253</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>46006</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45015</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>46256</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>46300</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46300</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46300</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46300</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>46300</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62003,7 +62003,7 @@
         <v>46255</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>46190</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>46260</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62222,7 +62222,7 @@
         <v>46260</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>46261</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>44713</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>44676</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>44501</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62587,7 +62587,7 @@
         <v>45617</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62660,7 +62660,7 @@
         <v>44970</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>45089</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44809</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>45440</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45677</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63030,7 +63030,7 @@
         <v>45677</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>45503</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45659</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>44784</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>44841</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>45012</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>44956</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>45069</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63614,7 +63614,7 @@
         <v>45120</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63687,7 +63687,7 @@
         <v>45728</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63760,7 +63760,7 @@
         <v>45702</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
         <v>45702</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45726</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63979,7 +63979,7 @@
         <v>45734</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64052,7 +64052,7 @@
         <v>45811</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>45811</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64198,7 +64198,7 @@
         <v>45811</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>45901</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>45945</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64417,7 +64417,7 @@
         <v>45946</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64490,7 +64490,7 @@
         <v>46127</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64563,7 +64563,7 @@
         <v>46141</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45357</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45925</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>46136</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45714</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44970</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>46213</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44494</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45244</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45492</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45465</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45315</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45303</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>46091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46013</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45016</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45622</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44910</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44767</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45665</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>46304</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>45799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45602</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>45577</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45738</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44686</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44767</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44840</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45930</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46150</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45328</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44767</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45958</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45009</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45352</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45128</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>45267</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45343</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45833</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45112</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45546</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45845</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45607</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>46189</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>45302</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>46188</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>44971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45842</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>46108</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45468</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45247</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>46287</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45015</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45506</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>46253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45446</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>45835</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45754</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45511</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>45274</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45295</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45574</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46058</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>46148</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44574</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44705</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>44838</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44533</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44536</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44670</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44725</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44560</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44672</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44705</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>44558</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44744</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>44767</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44609</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44628</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44572</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44607</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44592</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44627</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44888</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44744</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44491</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44862</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>44838</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44713</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44697</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44645</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44672</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44628</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45416</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45338</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45520</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45474</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45121</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45144</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>44645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45665</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45643</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44824</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45554</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45107</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>44744</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45419</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45577</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45307</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45132</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45544</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45342</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45110</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44743</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45300</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>44634</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45652</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45761</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44961</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45665</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45490</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44655</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45586</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45405</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45007</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45693</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45465</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45049</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45707</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45343</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45089</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45116</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45555</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45204</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45357</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45260</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45233</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45233</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45582</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45555</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44487</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44938</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45600</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45121</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45343</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45343</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45121</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45532</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45326</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45119</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>44513</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45496</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44742</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45561</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45323</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45532</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45532</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45446</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45338</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45577</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44572</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>44945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45477</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45168</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45727</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45085</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>44587</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45069</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45244</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45364</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44774</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45485</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45247</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44627</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45119</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45121</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45281</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44847</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45586</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45229</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>46136</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45887</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>44853</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45554</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45646</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44853</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45226</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45889</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45668</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>44855</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45895</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45895</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>45894</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45098</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45166</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45166</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45896</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44595</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45470</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45482</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45887</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45898</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45900</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45900</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45027</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45144</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45144</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45331</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45900</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>46141</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45338</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45900</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45900</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45755</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45083</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45900</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45412</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45737</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45035</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45644</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45792</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45915</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>45355</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45915</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>45083</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45198</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>44544</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45511</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>44846</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45589</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45577</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45554</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>46147</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45533</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45925</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45729</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45925</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45197</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>46149</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45103</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45930</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45933</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45915</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46153</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45190</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44984</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44858</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45939</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>46150</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45226</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45939</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45939</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45939</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44599</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>45939</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45134</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>44876</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44915</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45366</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45315</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45945</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45467</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45568</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45247</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45945</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>44795</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45723</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45002</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45755</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45953</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45328</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44904</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44847</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45954</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45954</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45960</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45898</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45803</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45426</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45453</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44918</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45887</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46030</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44579</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45972</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45973</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45386</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45377</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45737</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45738</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45978</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45979</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44866</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45370</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45370</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44923</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45187</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45985</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44993</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45600</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45343</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>44497</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45987</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45337</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44818</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45989</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44684</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45993</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45993</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45993</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45989</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45337</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45478</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45180</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45903</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45307</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44879</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45260</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45012</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>46001</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45568</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>45846</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>45763</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45700</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>45579</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45882</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>46008</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>45926</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45648</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44816</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45664</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45455</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45343</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45149</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>45938</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45232</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45311</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45072</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45573</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45803</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45144</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45586</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45526</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>46031</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>45709</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>44628</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>45712</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>46035</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>46036</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>46031</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>46041</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>46041</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>46177</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>46043</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45408</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46042</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46042</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45573</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>46043</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46043</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>46035</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45812</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45398</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45054</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45194</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>46048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45085</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44992</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>46181</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>46057</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45306</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45307</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45493</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45387</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>46069</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>46188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45474</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45189</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45282</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45274</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45737</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45265</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>46076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45894</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45831</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45668</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46083</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45894</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45894</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45882</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>46055</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>44893</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45902</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>44729</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46041</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46092</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45712</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46092</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46094</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>46094</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45336</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45420</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>46095</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45079</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45315</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45120</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>45307</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>45002</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45465</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45012</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46198</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45228</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46120</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45343</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>46120</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>46120</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>46120</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45042</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>46202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45672</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45338</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>46129</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45014</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44988</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45415</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>44998</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45019</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>45124</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>44497</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45338</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>46112</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>44894</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45465</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45461</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45191</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45300</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45301</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>45470</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>45098</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45608</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>44894</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45321</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>46212</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>46212</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>46212</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>46212</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45315</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>46214</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>45077</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>45077</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45566</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>44991</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45022</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>46218</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>46217</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>46222</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>45254</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>44963</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>46223</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45727</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45267</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45394</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45180</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45379</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>46273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>46271</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45282</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>46271</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49970,7 +49970,7 @@
         <v>45465</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>45544</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>45119</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>46272</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>46135</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45343</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45586</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>46276</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>46276</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>44923</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>46276</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>46237</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>45414</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45334</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45646</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45334</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>46276</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>46205</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51299,7 +51299,7 @@
         <v>46276</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         <v>46280</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>44972</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51523,7 +51523,7 @@
         <v>45303</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45476</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>45525</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45716</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45197</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45474</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>46271</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45253</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44767</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>44732</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44995</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45106</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>44596</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>46284</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>44992</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>46287</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52784,7 +52784,7 @@
         <v>46244</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>46287</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>46271</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45165</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>46287</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46288</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45149</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45182</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>46272</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>45247</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45310</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45110</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46287</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>46250</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>44933</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45685</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46289</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>46290</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>46250</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>45278</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45278</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45506</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>45119</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45141</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45141</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>44858</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45738</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>46272</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54868,7 +54868,7 @@
         <v>45090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54941,7 +54941,7 @@
         <v>45121</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45738</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45738</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45566</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45357</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>45622</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>45015</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>46296</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45189</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45387</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>46190</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55759,7 +55759,7 @@
         <v>44991</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>46253</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>46295</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>46253</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>46253</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>46253</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>46255</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>44907</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>45275</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>45119</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>46300</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>44694</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>44946</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45737</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>46300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45776</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45443</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>46256</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45574</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>46006</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>46300</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>46300</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45414</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>46300</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>46260</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>44497</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>45357</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>45370</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>45603</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57896,7 +57896,7 @@
         <v>45217</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57969,7 +57969,7 @@
         <v>45233</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45700</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45183</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>46260</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45517</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45498</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>46261</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45533</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45797</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>46189</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>45799</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45648</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>45800</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>45670</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45553</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>46308</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>46308</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45804</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45804</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>45810</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>45396</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>45810</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>46310</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59653,7 +59653,7 @@
         <v>44537</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>45420</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45843</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45737</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45831</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>45706</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45737</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45737</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45833</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45832</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60388,7 +60388,7 @@
         <v>45758</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>45440</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>45609</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45321</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45408</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45736</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>45014</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45736</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45706</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45715</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>45845</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>45818</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>45749</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45860</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>45827</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61483,7 +61483,7 @@
         <v>44712</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45874</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45874</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45874</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>44713</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45607</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45607</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>44607</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>45546</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62165,7 +62165,7 @@
         <v>45558</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62243,7 +62243,7 @@
         <v>45558</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>45418</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45581</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62477,7 +62477,7 @@
         <v>44501</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>45617</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>44970</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62701,7 +62701,7 @@
         <v>45089</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>44713</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62847,7 +62847,7 @@
         <v>44809</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62920,7 +62920,7 @@
         <v>45440</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         <v>45677</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63066,7 +63066,7 @@
         <v>45677</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63139,7 +63139,7 @@
         <v>45503</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63212,7 +63212,7 @@
         <v>45659</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63285,7 +63285,7 @@
         <v>44784</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>44841</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45012</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>44676</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>44956</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63650,7 +63650,7 @@
         <v>45069</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         <v>45120</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45728</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63869,7 +63869,7 @@
         <v>45702</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63942,7 +63942,7 @@
         <v>45702</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64015,7 +64015,7 @@
         <v>45726</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64088,7 +64088,7 @@
         <v>45734</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64161,7 +64161,7 @@
         <v>45811</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45811</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64307,7 +64307,7 @@
         <v>45811</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64380,7 +64380,7 @@
         <v>45901</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64453,7 +64453,7 @@
         <v>45945</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64526,7 +64526,7 @@
         <v>45946</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>46127</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64672,7 +64672,7 @@
         <v>46141</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>45677</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45663</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45357</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45925</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45336</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>46136</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>46133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45069</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44823</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45946</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>45128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45714</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44970</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>46213</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44494</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45244</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45492</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45465</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45315</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45303</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>46091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46013</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45016</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45622</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44910</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44767</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45665</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>46304</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>45799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45602</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>45577</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45738</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44686</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44767</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44840</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45930</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46150</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45328</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44767</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45958</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45009</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45352</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45128</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>45267</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45343</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45833</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45112</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45546</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45845</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45607</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>46189</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>45302</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>46188</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>44971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45842</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>46108</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45468</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45247</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>46287</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45015</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45506</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>46253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45446</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>45835</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45754</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45511</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>45274</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45295</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45574</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46058</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>46148</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44574</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44705</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>44838</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44533</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44536</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44670</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44725</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44560</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44672</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44705</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>44558</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44744</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>44767</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44609</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44628</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44572</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44607</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44592</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44627</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44888</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44744</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44491</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44862</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>44838</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44713</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44697</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44645</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44672</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44628</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45416</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45338</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45520</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45474</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45121</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45144</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>44645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45665</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45643</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44824</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45554</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45107</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>44744</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45419</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45577</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45307</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45132</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45544</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45342</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45110</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44743</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45300</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>44634</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45652</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45761</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44961</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45665</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45490</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44655</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45586</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45405</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45007</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45693</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45465</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45049</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45707</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45343</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45089</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45116</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45555</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45204</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45357</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45260</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45233</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45233</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45582</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45555</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44487</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44938</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45600</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45121</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45343</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45343</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45121</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45532</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45326</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45119</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>44513</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45496</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44742</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45561</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45323</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45532</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45532</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45446</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45338</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45577</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44572</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>44945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45477</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45168</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45727</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45085</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>44587</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45069</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45244</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45364</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44774</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45485</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45247</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44627</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45119</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45121</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45281</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44847</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45586</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45229</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>46136</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45887</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>44853</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45554</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45646</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44853</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45226</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45889</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45668</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>44855</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45895</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45895</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>45894</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45098</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45166</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45166</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45896</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44595</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45470</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45482</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45887</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45898</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45900</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45900</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45027</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45144</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45144</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45331</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45900</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>46141</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45338</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45900</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45900</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45755</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45083</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45900</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45412</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45737</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45035</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45644</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45792</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45915</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>45355</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45915</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>45083</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45198</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>44544</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45511</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>44846</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45589</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45577</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45554</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>46147</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45533</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45925</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45729</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45925</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45197</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>46149</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45103</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45930</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45933</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45915</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46153</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45190</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44984</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44858</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45939</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>46150</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45226</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45939</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45939</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45939</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44599</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>45939</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45134</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>44876</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44915</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45366</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45315</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45945</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45467</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45568</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45247</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45945</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>44795</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45723</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45002</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45755</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45953</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45328</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44904</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44847</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45954</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45954</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45960</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45898</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45803</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45426</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45453</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44918</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45887</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46030</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44579</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45972</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45973</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45386</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45377</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45737</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45738</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45978</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45979</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44866</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45370</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45370</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44923</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45187</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45985</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44993</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45600</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45343</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>44497</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45987</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45337</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44818</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45989</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44684</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45993</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45993</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45993</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45989</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45337</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45478</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45180</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45903</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45307</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44879</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45260</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45012</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>46001</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45568</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>45846</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>45763</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45700</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>45579</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45882</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>46008</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>45926</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45648</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44816</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45664</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45455</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45343</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45149</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>45938</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45232</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45311</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45072</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45573</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45803</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45144</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45586</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45526</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>46031</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>45709</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>44628</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>45712</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>46035</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>46036</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>46031</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>46041</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>46041</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>46177</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>46043</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45408</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46042</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46042</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45573</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>46043</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46043</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>46035</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45812</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45398</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45054</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45194</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>46048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45085</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44992</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>46181</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>46057</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45306</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45307</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45493</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45387</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>46069</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>46188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45474</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45189</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45282</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45274</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45737</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45265</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>46076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45894</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45831</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45668</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46083</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45894</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45894</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45882</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>46055</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>44893</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45902</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>44729</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46041</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46092</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45712</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46092</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46094</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>46094</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45336</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45420</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>46095</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45079</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45315</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45120</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>45307</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>45002</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45465</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45012</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46198</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45228</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46120</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45343</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>46120</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>46120</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>46120</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45042</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>46202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45672</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45338</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>46129</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45014</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44988</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45415</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>44998</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45019</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>45124</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>44497</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45338</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>46112</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>44894</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45465</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45461</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45191</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45300</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45301</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>45470</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>45098</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45608</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>44894</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45321</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>46212</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>46212</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>46212</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>46212</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45315</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>46214</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>45077</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>45077</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45566</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>44991</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45022</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>46218</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>46217</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>46222</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>45254</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>44963</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>46223</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45727</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45267</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45394</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45180</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45379</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>46273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>46271</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45282</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>46271</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49970,7 +49970,7 @@
         <v>45465</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>45544</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>45119</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>46272</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>46135</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45343</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45586</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>46276</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>46276</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>44923</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>46276</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>46237</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>45414</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45334</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45646</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45334</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>46276</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>46205</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51299,7 +51299,7 @@
         <v>46276</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         <v>46280</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>44972</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51523,7 +51523,7 @@
         <v>45303</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45476</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>45525</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45716</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45197</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45474</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>46271</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45253</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44767</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>44732</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44995</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45106</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>44596</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>46284</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>44992</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>46287</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52784,7 +52784,7 @@
         <v>46244</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>46287</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>46271</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45165</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>46287</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46288</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45149</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45182</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>46272</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>45247</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45310</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45110</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46287</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>46250</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>44933</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45685</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46289</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>46290</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>46250</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>45278</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45278</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45506</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>45119</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45141</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45141</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>44858</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45738</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>46272</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54868,7 +54868,7 @@
         <v>45090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54941,7 +54941,7 @@
         <v>45121</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45738</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45738</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45566</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45357</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>45622</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>45015</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>46296</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45189</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45387</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>46190</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55759,7 +55759,7 @@
         <v>44991</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>46253</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>46295</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>46253</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>46253</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>46253</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>46255</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>44907</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>45275</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>45119</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>46300</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>44694</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>44946</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45737</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>46300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45776</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45443</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>46256</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45574</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>46006</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>46300</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>46300</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45414</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>46300</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>46260</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>44497</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>45357</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>45370</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>45603</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57896,7 +57896,7 @@
         <v>45217</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57969,7 +57969,7 @@
         <v>45233</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45700</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45183</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>46260</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45517</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45498</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>46261</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45533</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45797</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>46189</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>45799</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45648</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>45800</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>45670</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45553</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>46308</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>46308</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45804</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45804</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>45810</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>45396</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>45810</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>46310</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59653,7 +59653,7 @@
         <v>44537</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>45420</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45843</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45737</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45831</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>45706</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45737</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45737</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45833</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45832</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60388,7 +60388,7 @@
         <v>45758</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>45440</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>45609</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45321</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45408</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45736</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>45014</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45736</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45706</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45715</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>45845</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>45818</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>45749</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45860</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>45827</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61483,7 +61483,7 @@
         <v>44712</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45874</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45874</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45874</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>44713</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45607</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45607</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>44607</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>45546</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62165,7 +62165,7 @@
         <v>45558</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62243,7 +62243,7 @@
         <v>45558</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>45418</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45581</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62477,7 +62477,7 @@
         <v>44501</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>45617</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>44970</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62701,7 +62701,7 @@
         <v>45089</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>44713</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62847,7 +62847,7 @@
         <v>44809</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62920,7 +62920,7 @@
         <v>45440</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         <v>45677</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63066,7 +63066,7 @@
         <v>45677</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63139,7 +63139,7 @@
         <v>45503</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63212,7 +63212,7 @@
         <v>45659</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63285,7 +63285,7 @@
         <v>44784</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>44841</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45012</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>44676</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>44956</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63650,7 +63650,7 @@
         <v>45069</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         <v>45120</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45728</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63869,7 +63869,7 @@
         <v>45702</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63942,7 +63942,7 @@
         <v>45702</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64015,7 +64015,7 @@
         <v>45726</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64088,7 +64088,7 @@
         <v>45734</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64161,7 +64161,7 @@
         <v>45811</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45811</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64307,7 +64307,7 @@
         <v>45811</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64380,7 +64380,7 @@
         <v>45901</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64453,7 +64453,7 @@
         <v>45945</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64526,7 +64526,7 @@
         <v>45946</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>46127</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64672,7 +64672,7 @@
         <v>46141</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46314</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>45677</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45663</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45911</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45646</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45336</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45267</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45020</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45755</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45106</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44823</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45940</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>45470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>46301</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45671</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44970</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>46213</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44494</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45244</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45089</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45303</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>46013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44767</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45465</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45665</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>46304</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>46091</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45492</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44910</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45716</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45622</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45315</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>46091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44767</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>45930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45357</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45938</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45128</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45093</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45958</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45842</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>46189</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45468</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45748</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45993</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45139</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45477</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45265</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45446</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>46287</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45946</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45845</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45812</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>46253</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45835</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45506</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45754</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>46108</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44840</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45511</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>46134</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45577</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>46279</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44971</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45738</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44825</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45015</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45343</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45607</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45009</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45558</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45546</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45755</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44686</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45267</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45328</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45352</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45302</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44767</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>46058</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44670</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44536</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44705</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44560</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44744</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>44767</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44609</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44572</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44627</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44862</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44697</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>44601</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>44998</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45646</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>44672</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45887</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45887</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45197</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45197</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44742</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45072</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45337</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44846</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45895</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45043</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45532</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45532</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45233</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45233</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45300</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45331</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45343</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45476</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45900</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45900</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44858</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45900</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44732</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45900</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45232</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44743</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44767</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45737</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45229</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44879</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45887</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45465</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45496</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45426</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45470</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44876</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44684</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>44628</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45321</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44893</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45379</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45925</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45903</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45925</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45755</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46169</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45930</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45664</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45336</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45882</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45416</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45579</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45938</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45926</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44923</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45933</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45915</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44847</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45310</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>44991</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>44645</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45939</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45939</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45939</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45307</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45568</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45085</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45049</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46177</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45370</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45945</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45370</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45420</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45357</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45144</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45945</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45945</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45533</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45532</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46181</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45520</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44945</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44963</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45526</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45247</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45953</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45954</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45954</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45258</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45116</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45190</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45960</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45902</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>46041</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45189</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45803</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45121</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45506</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45668</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45712</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45306</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45019</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45973</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44933</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45197</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>46198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45149</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45002</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45648</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45307</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45467</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45121</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45144</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45144</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45979</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44774</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>44866</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46202</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45334</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46112</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45685</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45737</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45477</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45737</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45738</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45000</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45644</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45554</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45343</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45490</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45554</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45386</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45134</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45106</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45989</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45194</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46212</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>46214</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>46212</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>46212</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45323</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45993</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45993</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45586</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45993</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45544</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>46217</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45377</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45465</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45364</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>46218</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45646</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45846</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45776</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45568</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45470</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>46222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46001</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46135</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45443</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>44497</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45217</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45357</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46007</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45233</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45414</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>46237</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45370</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>46280</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>45574</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45803</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45700</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45603</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45183</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>46031</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>44818</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45517</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>46284</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46035</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45419</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46036</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46031</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45498</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>46042</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>46042</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46287</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46041</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>46041</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46043</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46287</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46043</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>46035</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46043</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46043</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45797</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45533</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46048</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>46287</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>46287</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46288</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>45670</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45799</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45648</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45553</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45804</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45800</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45804</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45396</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46057</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45810</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46290</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45810</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>46250</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46250</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45420</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>46069</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>44537</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46076</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46253</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46295</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45843</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46296</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>46083</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45706</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46253</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45737</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45832</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45894</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45894</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45737</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>46253</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46006</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45282</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45737</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>45882</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45831</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45894</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45015</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46256</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>45833</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45440</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46300</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>45758</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>46092</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>46300</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>46300</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>46300</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>46092</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>46094</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46300</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>46095</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>46094</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>46255</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45321</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45408</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45715</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45736</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45845</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45706</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45736</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>45609</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>46260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>46260</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45485</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45749</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45818</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>46111</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45860</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45337</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45827</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>44497</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44712</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>46261</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45511</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46120</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>46120</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>46120</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>46120</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>45874</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45874</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>45874</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>46308</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46129</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45303</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>44713</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45418</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45546</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45581</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45607</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45558</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45558</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>44607</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45737</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45777</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45589</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45573</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>44993</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>46308</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>46189</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45482</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45749</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44995</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44938</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>44853</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45408</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>44599</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46136</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46271</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>46314</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>46271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>46271</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45120</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45461</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45412</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>46310</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45103</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>46271</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45338</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>44923</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>44853</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45577</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45198</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>44894</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45042</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>46272</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>46273</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>46272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>46272</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45338</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46310</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45583</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>46289</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>46141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>46276</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>46276</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>46314</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>46244</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46276</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>46276</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45544</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>44946</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>44744</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45228</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>46147</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>44988</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45085</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>46149</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>46150</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45525</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49396,7 +49396,7 @@
         <v>45398</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46153</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45107</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45343</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>45586</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>45712</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45343</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45723</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>44634</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45355</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45180</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>46030</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44579</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45121</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45121</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45453</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45112</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45577</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45307</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45600</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>44995</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45079</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45166</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45672</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45012</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45077</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>45077</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45144</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45119</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>44992</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45275</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45166</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45465</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>45014</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45357</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45668</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44795</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>45187</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45693</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45455</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45707</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45709</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45544</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>45089</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>45110</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>45247</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45554</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45022</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45027</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45334</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45738</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45197</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45083</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45474</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>44918</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45012</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45054</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>44991</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45465</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45069</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45226</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>44846</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45098</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45119</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45260</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45555</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45493</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45342</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>45738</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45738</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45311</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45307</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45761</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45582</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45366</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45446</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45716</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45566</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>44894</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55218,7 +55218,7 @@
         <v>45727</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45343</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45247</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45119</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>45098</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>45478</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45600</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45002</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>45326</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>45544</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>44824</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45121</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45281</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>44544</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45387</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45394</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45338</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56469,7 +56469,7 @@
         <v>45577</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45007</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56615,7 +56615,7 @@
         <v>45474</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>45180</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45643</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>45149</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45260</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45168</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>44587</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>45278</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>44904</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>45561</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>45127</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45315</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>45755</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>45124</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45414</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>44596</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>45729</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45586</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45586</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>45159</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45338</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>44627</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58241,7 +58241,7 @@
         <v>45573</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45049</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45727</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45119</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45555</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>45189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>45165</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>45110</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58840,7 +58840,7 @@
         <v>45622</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45665</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45141</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45141</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59132,7 +59132,7 @@
         <v>45083</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59210,7 +59210,7 @@
         <v>45090</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>45665</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>44694</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45204</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45132</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59575,7 +59575,7 @@
         <v>45415</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45700</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>44655</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>45387</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45188</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59940,7 +59940,7 @@
         <v>44729</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45119</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60086,7 +60086,7 @@
         <v>45244</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45278</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>44858</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>44816</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45173</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>45300</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45315</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60602,7 +60602,7 @@
         <v>45315</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>45328</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>44817</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>45338</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45343</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45343</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>44855</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45474</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45356</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>44961</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>44907</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>44595</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44497</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45267</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>45282</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>45301</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61785,7 +61785,7 @@
         <v>45265</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45226</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45405</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>44847</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45254</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62150,7 +62150,7 @@
         <v>45191</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>45652</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62296,7 +62296,7 @@
         <v>44513</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62369,7 +62369,7 @@
         <v>45274</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>45566</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62515,7 +62515,7 @@
         <v>44972</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>44713</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>44676</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>44501</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45617</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>44970</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62958,7 +62958,7 @@
         <v>45089</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>44809</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45440</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>45677</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63250,7 +63250,7 @@
         <v>45677</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63323,7 +63323,7 @@
         <v>45503</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45659</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63469,7 +63469,7 @@
         <v>44784</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63542,7 +63542,7 @@
         <v>44841</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63615,7 +63615,7 @@
         <v>45012</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>44956</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63761,7 +63761,7 @@
         <v>45069</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
         <v>45120</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45728</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63980,7 +63980,7 @@
         <v>45702</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45702</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45726</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45734</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45811</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>45811</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45811</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45901</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>45945</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>45946</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>46127</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>46141</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46314</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>45677</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45663</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45911</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45646</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45336</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45267</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45020</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45755</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45106</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44823</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45940</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>45470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>46301</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45671</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44970</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>46213</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44494</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45244</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45089</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45303</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>46013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44767</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45465</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45665</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>46304</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>46091</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45492</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44910</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45716</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45622</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45315</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>46091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44767</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>45930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45357</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45938</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45128</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45093</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45958</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45842</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>46189</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45468</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45748</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45993</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45139</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45477</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45265</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45446</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>46287</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45946</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45845</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45812</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>46253</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45835</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45506</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45754</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>46108</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44840</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45511</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>46134</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45577</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>46279</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44971</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45738</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44825</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45015</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45343</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45607</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45009</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45558</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45546</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45755</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44686</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45267</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45328</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45352</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45302</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44767</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>46058</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44670</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44536</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44705</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44560</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44744</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>44767</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44609</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44572</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44627</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44862</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44697</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>44601</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>44998</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45646</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>44672</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45887</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45887</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45197</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45197</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44742</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45072</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45337</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44846</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45895</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45043</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45532</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45532</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45233</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45233</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45300</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45331</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45343</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45476</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45900</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45900</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44858</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45900</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44732</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45900</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45232</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44743</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44767</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45737</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45229</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44879</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45887</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45465</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45496</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45426</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45470</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44876</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44684</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>44628</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45321</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44893</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45379</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45925</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45903</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45925</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45755</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46169</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45930</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45664</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45336</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45882</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45416</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45579</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45938</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45926</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44923</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45933</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45915</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44847</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45310</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>44991</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>44645</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45939</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45939</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45939</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45307</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45568</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45085</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45049</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46177</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45370</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45945</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45370</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45420</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45357</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45144</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45945</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45945</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45533</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45532</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46181</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45520</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44945</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44963</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45526</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45247</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45953</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45954</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45954</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45258</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45116</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45190</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45960</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45902</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>46041</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45189</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45803</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45121</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45506</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45668</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45712</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45306</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45019</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45973</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44933</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45197</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>46198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45149</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45002</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45648</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45307</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45467</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45121</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45144</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45144</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45979</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44774</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>44866</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46202</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45334</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46112</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45685</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45737</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45477</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45737</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45738</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45000</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45644</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45554</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45343</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45490</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45554</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45386</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45134</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45106</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45989</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45194</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46212</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>46214</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>46212</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>46212</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45323</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45993</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45993</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45586</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45993</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45544</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>46217</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45377</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45465</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45364</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>46218</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45646</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45846</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45776</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45568</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45470</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>46222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46001</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46135</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45443</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>44497</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45217</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45357</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46007</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45233</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45414</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>46237</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45370</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>46280</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>45574</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45803</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45700</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45603</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45183</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>46031</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>44818</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45517</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>46284</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46035</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45419</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46036</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46031</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45498</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>46042</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>46042</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46287</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46041</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>46041</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46043</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46287</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46043</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>46035</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46043</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46043</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45797</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45533</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46048</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>46287</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>46287</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46288</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>45670</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45799</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45648</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45553</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45804</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45800</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45804</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45396</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46057</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45810</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46290</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45810</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>46250</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46250</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45420</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>46069</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>44537</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46076</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46253</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46295</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45843</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46296</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>46083</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45706</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46253</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45737</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45832</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45894</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45894</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45737</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>46253</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46006</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45282</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45737</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>45882</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45831</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45894</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45015</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46256</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>45833</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45440</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46300</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>45758</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>46092</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>46300</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>46300</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>46300</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>46092</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>46094</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46300</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>46095</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>46094</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>46255</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45321</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45408</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45715</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45736</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45845</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45706</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45736</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>45609</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>46260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>46260</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45485</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45749</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45818</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>46111</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45860</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45337</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45827</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>44497</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44712</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>46261</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45511</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46120</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>46120</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>46120</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>46120</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>45874</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45874</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>45874</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>46308</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46129</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45303</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>44713</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45418</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45546</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45581</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45607</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45558</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45558</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>44607</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45737</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45777</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45589</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45573</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>44993</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>46308</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>46189</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45482</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45749</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44995</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44938</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>44853</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45408</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>44599</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46136</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46271</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>46314</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>46271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>46271</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45120</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45461</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45412</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>46310</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45103</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>46271</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45338</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>44923</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>44853</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45577</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45198</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>44894</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45042</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>46272</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>46273</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>46272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>46272</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45338</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46310</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45583</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>46289</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>46141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>46276</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>46276</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>46314</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>46244</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46276</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>46276</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45544</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>44946</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>44744</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45228</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>46147</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>44988</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45085</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>46149</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>46150</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45525</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49396,7 +49396,7 @@
         <v>45398</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46153</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45107</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45343</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>45586</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>45712</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45343</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45723</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>44634</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45355</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45180</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>46030</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44579</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45121</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45121</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45453</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45112</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45577</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45307</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45600</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>44995</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45079</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45166</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45672</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45012</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45077</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>45077</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45144</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45119</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>44992</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45275</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45166</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45465</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>45014</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45357</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45668</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44795</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>45187</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45693</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45455</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45707</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45709</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45544</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>45089</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>45110</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>45247</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45554</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45022</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45027</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45334</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45738</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45197</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45083</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45474</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>44918</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45012</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45054</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>44991</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45465</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45069</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45226</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>44846</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45098</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45119</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45260</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45555</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45493</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45342</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>45738</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45738</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45311</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45307</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45761</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45582</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45366</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45446</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45716</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45566</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>44894</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55218,7 +55218,7 @@
         <v>45727</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45343</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45247</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45119</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>45098</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>45478</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45600</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45002</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>45326</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>45544</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>44824</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45121</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45281</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>44544</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45387</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45394</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45338</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56469,7 +56469,7 @@
         <v>45577</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45007</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56615,7 +56615,7 @@
         <v>45474</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>45180</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45643</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>45149</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45260</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45168</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>44587</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>45278</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>44904</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>45561</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>45127</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45315</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>45755</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>45124</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45414</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>44596</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>45729</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45586</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45586</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>45159</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45338</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>44627</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58241,7 +58241,7 @@
         <v>45573</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45049</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45727</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45119</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45555</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>45189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>45165</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>45110</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58840,7 +58840,7 @@
         <v>45622</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45665</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45141</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45141</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59132,7 +59132,7 @@
         <v>45083</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59210,7 +59210,7 @@
         <v>45090</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>45665</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>44694</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45204</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45132</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59575,7 +59575,7 @@
         <v>45415</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45700</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>44655</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>45387</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45188</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59940,7 +59940,7 @@
         <v>44729</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45119</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60086,7 +60086,7 @@
         <v>45244</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45278</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>44858</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>44816</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45173</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>45300</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45315</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60602,7 +60602,7 @@
         <v>45315</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>45328</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>44817</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>45338</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45343</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45343</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>44855</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45474</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45356</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>44961</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>44907</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>44595</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44497</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45267</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>45282</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>45301</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61785,7 +61785,7 @@
         <v>45265</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45226</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45405</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>44847</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45254</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62150,7 +62150,7 @@
         <v>45191</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>45652</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62296,7 +62296,7 @@
         <v>44513</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62369,7 +62369,7 @@
         <v>45274</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>45566</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62515,7 +62515,7 @@
         <v>44972</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>44713</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>44676</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>44501</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45617</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>44970</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62958,7 +62958,7 @@
         <v>45089</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>44809</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45440</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>45677</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63250,7 +63250,7 @@
         <v>45677</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63323,7 +63323,7 @@
         <v>45503</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45659</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63469,7 +63469,7 @@
         <v>44784</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63542,7 +63542,7 @@
         <v>44841</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63615,7 +63615,7 @@
         <v>45012</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>44956</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63761,7 +63761,7 @@
         <v>45069</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
         <v>45120</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45728</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63980,7 +63980,7 @@
         <v>45702</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45702</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45726</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45734</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45811</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>45811</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45811</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45901</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>45945</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>45946</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>46127</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>46141</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46314</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>45677</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45663</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45357</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45646</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45336</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45303</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46157</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44823</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45940</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>45470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45714</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>46301</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44970</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>46213</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45244</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45492</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45465</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45315</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45303</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>46091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45089</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45716</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>46013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45622</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44910</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44767</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45665</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46304</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>45577</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44743</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>44686</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45738</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44767</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45833</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45938</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45477</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45946</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45511</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>45845</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45755</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45607</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45985</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45748</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45993</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45328</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44767</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45352</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46108</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45128</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>45558</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45267</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45343</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>46134</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45607</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45302</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44971</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45468</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45477</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>46189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45842</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45247</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44825</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45015</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45506</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>46287</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45446</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>46253</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46323</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>46058</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44536</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44670</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44725</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44560</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44705</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44744</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44767</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44609</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44572</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>44837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44627</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44862</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>44697</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44672</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45416</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45338</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45520</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45474</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45121</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45144</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44645</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45643</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45127</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45554</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45419</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45577</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45307</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45198</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45132</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44846</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45110</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44744</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45544</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45342</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45652</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45761</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44634</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45665</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45300</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45586</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45693</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45490</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44961</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45465</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>44743</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45405</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45007</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44655</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45343</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45707</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45544</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45357</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45116</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45555</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45204</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45260</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45089</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45173</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45555</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45799</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45887</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45648</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45800</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45670</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45553</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45343</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45343</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45233</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45233</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45582</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45600</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45804</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45804</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45121</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45544</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45810</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45532</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45396</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46031</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45244</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44627</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45586</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45229</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45889</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>44537</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45326</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45420</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45496</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45119</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>46035</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>44513</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45895</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44984</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45894</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45896</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45561</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45532</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45532</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45338</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45577</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44572</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45898</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45900</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45900</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>46036</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>46031</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46041</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45323</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45900</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>46041</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44742</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45900</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45900</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45446</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>46043</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46042</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45843</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>46043</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>46043</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>46043</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45737</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>46043</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>46035</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45831</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45706</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45737</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45737</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45900</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45737</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45833</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45477</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45832</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45727</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45758</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45440</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45792</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45915</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45085</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45915</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44817</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45609</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45321</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>44587</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45408</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45736</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45014</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45736</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45706</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45069</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45715</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45845</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45364</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45818</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45925</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45749</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45925</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45925</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>44774</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>46048</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45247</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45860</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45485</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45930</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45827</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44712</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45931</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45933</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45121</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45915</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45583</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>44847</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45939</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45874</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45874</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45874</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45554</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45939</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45939</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45939</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>45939</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>45945</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45568</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>44713</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45607</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>45607</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45945</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>44607</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45546</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45558</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45558</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45418</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>46057</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45581</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45226</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45668</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44855</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45646</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>45166</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45166</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45258</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>44595</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>45470</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>45953</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45027</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45144</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45144</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45331</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45338</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>46069</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45954</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45954</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45958</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45755</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45083</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45960</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45035</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45644</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45803</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45159</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45355</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45083</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44544</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45511</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44846</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>46076</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45589</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45577</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45554</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45973</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>45972</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45973</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45533</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45729</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45197</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45894</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45978</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>45979</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46083</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45894</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45894</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45103</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45882</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44984</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44858</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45226</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44599</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45987</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45134</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44876</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44915</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45366</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45315</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45467</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45247</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>44995</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45993</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45993</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45993</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45989</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44795</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45002</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45755</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45328</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>46092</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>44904</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>46092</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>46094</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46094</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45426</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>46001</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44918</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45568</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45846</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46095</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>46007</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45049</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>46008</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45386</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45377</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45737</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45738</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44866</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45370</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45370</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>44923</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45187</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45803</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44993</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45600</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45343</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45337</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>44818</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>46111</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44684</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>45337</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46120</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>46120</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>46120</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45478</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>46120</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45180</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45307</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45197</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>44879</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45260</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>45012</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>46129</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45700</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45648</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>44816</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45664</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>45455</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>45343</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45149</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45232</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45338</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>45311</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45072</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45573</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45144</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45586</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45461</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45526</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>46136</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45709</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>44628</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45712</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45408</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45777</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45573</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45398</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45749</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45054</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45194</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>45085</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>44992</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45482</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45306</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45307</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45493</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45387</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45474</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46141</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45282</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45274</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45737</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45265</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45412</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>44893</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>44729</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>46147</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45336</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>45420</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46149</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45079</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45315</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45120</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45307</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45002</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46153</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46150</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45465</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45012</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>45723</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45228</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45343</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45874</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45898</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45453</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45887</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>46030</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45042</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44579</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45672</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45338</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45014</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>44988</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45415</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>44998</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45019</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45124</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>46169</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45903</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>44894</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>45465</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>45763</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45191</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45300</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45301</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45579</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45882</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45926</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>45470</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45938</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45098</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45608</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>44894</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45321</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45315</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>45077</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45077</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>46177</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45566</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>44991</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45022</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45812</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45254</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>44963</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46181</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45727</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45394</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45180</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>45379</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>45282</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45465</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45544</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45119</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45343</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45668</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>46055</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45902</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>46041</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45586</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45712</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44923</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45414</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45334</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45646</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45334</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>44972</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45303</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46198</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>45476</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>45525</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45716</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>45043</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46202</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45197</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>46112</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45474</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45253</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>44767</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>44732</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>44995</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>45106</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>44596</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>44992</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46212</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>46212</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>46212</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46212</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>46214</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45165</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>46218</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>45149</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>45182</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>46217</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45247</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>46222</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45310</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>45110</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55109,7 +55109,7 @@
         <v>46223</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>44933</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45685</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>46135</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>46237</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>46205</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45278</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45278</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45506</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45141</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45141</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>44858</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45738</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>45090</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45121</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45738</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56355,7 +56355,7 @@
         <v>45738</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>45566</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>45357</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>45622</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45189</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45387</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>46284</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46287</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>44991</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>44907</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>46287</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57178,7 +57178,7 @@
         <v>45275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45119</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>44694</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57402,7 +57402,7 @@
         <v>44946</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46287</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45737</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46288</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>45776</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>46287</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>46250</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45443</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45574</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>46290</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45414</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>46250</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>45357</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58371,7 +58371,7 @@
         <v>45370</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45603</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45217</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>45233</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>45700</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58736,7 +58736,7 @@
         <v>45183</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45517</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>45498</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45015</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46296</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45533</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45797</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>46190</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59325,7 +59325,7 @@
         <v>46253</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>46295</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>46253</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>46253</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>46253</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>46255</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>46300</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46256</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>46006</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>46300</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>46300</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>46300</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46260</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46260</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>46261</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>46189</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>46308</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>46308</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>46272</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>46272</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>46271</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>46271</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>46271</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46271</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46314</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>46272</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46310</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>46273</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>46314</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>46276</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46289</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46276</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46276</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46276</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>46244</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>46321</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>46280</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>46321</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62212,7 +62212,7 @@
         <v>46310</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62285,7 +62285,7 @@
         <v>44853</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62363,7 +62363,7 @@
         <v>44501</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45617</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62509,7 +62509,7 @@
         <v>44970</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62587,7 +62587,7 @@
         <v>45089</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62660,7 +62660,7 @@
         <v>44713</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62733,7 +62733,7 @@
         <v>44809</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62806,7 +62806,7 @@
         <v>45440</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         <v>45677</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62952,7 +62952,7 @@
         <v>45677</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63025,7 +63025,7 @@
         <v>45503</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63098,7 +63098,7 @@
         <v>45659</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>44784</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>44841</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63317,7 +63317,7 @@
         <v>45012</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63390,7 +63390,7 @@
         <v>44676</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>44956</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63536,7 +63536,7 @@
         <v>45069</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         <v>45120</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63682,7 +63682,7 @@
         <v>45728</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63755,7 +63755,7 @@
         <v>45702</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63828,7 +63828,7 @@
         <v>45702</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63901,7 +63901,7 @@
         <v>45726</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>45734</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64047,7 +64047,7 @@
         <v>45811</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45811</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>45811</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         <v>45901</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64339,7 +64339,7 @@
         <v>45945</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64412,7 +64412,7 @@
         <v>45946</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>46127</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64558,7 +64558,7 @@
         <v>46141</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>

--- a/Översikt KRISTIANSTAD.xlsx
+++ b/Översikt KRISTIANSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45107</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44587</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46314</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>45677</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45663</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45357</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45646</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45925</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45336</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45303</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46157</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44823</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45940</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>45470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45946</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45714</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45952</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46132</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>46301</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44970</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>46213</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45244</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45492</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45465</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45315</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45303</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>46091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45089</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45716</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>46013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45622</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44910</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44767</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45665</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46304</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>45577</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44743</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>44686</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45738</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44767</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45833</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45938</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45477</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45946</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45511</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>45845</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45755</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45607</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45985</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45748</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45993</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45328</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44767</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45352</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46108</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45128</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>45558</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45267</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45343</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>46134</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45607</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45302</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44971</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45468</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45477</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>46189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45842</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45247</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44825</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45015</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45506</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>46287</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45446</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>46253</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46323</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45274</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45736</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>46058</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44705</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44536</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44670</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44672</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44725</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44560</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44705</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44744</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44767</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44609</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44628</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44572</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>44837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44627</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44862</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44767</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44749</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44518</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>44697</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44672</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45416</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45338</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45520</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45474</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45121</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45144</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44645</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45643</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45127</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45554</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45419</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45577</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45307</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45198</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45132</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44846</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45110</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44744</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45544</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45342</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45652</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45761</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44634</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45665</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45300</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45586</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45693</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45490</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44961</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45465</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>44743</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45405</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45007</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44655</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45343</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45707</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45544</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45357</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45116</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45555</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45204</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45260</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45089</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45173</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45555</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45799</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45887</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45648</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45800</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45670</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45553</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45343</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45343</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45233</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45233</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45582</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45600</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45804</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45804</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45121</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45544</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45810</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45532</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45396</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46031</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45244</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44627</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45586</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45229</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45889</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>44537</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45326</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45420</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45496</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45119</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>46035</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>44513</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45895</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44984</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45894</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45896</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45561</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45532</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45532</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45338</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45577</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44572</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45898</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45900</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45900</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>46036</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>46031</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46041</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45323</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45900</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>46041</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44742</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45900</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45900</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45446</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>46043</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46042</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45843</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>46043</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>46043</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>46043</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45737</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>46043</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>46035</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45831</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45706</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45737</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45737</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45900</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45737</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45833</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45477</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45832</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45727</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45758</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45440</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45792</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45915</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45085</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45915</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44817</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45609</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45321</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>44587</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45408</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45736</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45014</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45736</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45706</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45069</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45715</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45845</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45364</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45818</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45925</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45749</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45925</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45925</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>44774</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>46048</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45247</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45860</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45485</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45930</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45827</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44712</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45931</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45933</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45121</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45915</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45583</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>44847</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45939</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45874</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45874</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45874</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45554</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45939</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45939</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45939</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>45939</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>45945</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45568</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>44713</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45607</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>45607</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45945</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>44607</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45546</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45558</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45558</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45418</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>46057</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45581</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45226</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45668</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44855</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45646</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>45166</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45166</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45258</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>44595</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>45470</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>45953</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45027</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45144</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45144</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45331</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45338</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>46069</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45954</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45954</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45958</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45755</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45083</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45960</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45035</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45644</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45803</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45159</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45355</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45083</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44544</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45511</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44846</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>46076</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45589</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45577</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45554</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45973</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>45972</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45973</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45533</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45729</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45197</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45894</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45978</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>45979</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46083</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45894</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45894</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45103</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45882</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44984</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44858</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45226</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44599</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45987</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45134</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44876</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44915</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45366</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45315</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45467</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45247</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>44995</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45993</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45993</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45993</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45989</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44795</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45002</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45755</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45328</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>46092</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>44904</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>46092</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>46094</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46094</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45426</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>46001</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44918</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45568</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45846</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46095</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>46007</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45049</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>46008</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45386</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45377</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45737</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45738</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44866</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45370</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45370</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>44923</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45187</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45803</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44993</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45600</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45343</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45337</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>44818</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>46111</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44684</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>45337</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46120</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>46120</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>46120</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45478</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>46120</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45180</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45307</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45197</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>44879</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45260</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>45012</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>46129</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45700</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45648</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>44816</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45664</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>45455</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>45343</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45149</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45232</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45338</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>45311</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45072</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45573</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45144</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45586</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45461</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45526</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>46136</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45709</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>44628</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45712</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45408</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45777</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45573</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45398</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45749</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45054</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45194</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>45085</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>44992</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45482</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45306</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45307</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45493</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45387</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45474</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46141</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45282</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45274</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45737</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45265</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45412</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>44893</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>44729</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>46147</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45336</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>45420</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46149</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45079</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45315</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45120</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45307</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45002</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46153</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46150</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45465</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45012</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>45723</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45228</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45343</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45874</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45898</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45453</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45887</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>46030</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45042</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44579</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45672</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45338</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45014</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>44988</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45415</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>44998</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45019</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45124</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>46169</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45903</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>44894</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>45465</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>45763</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45191</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45300</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45301</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45579</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45882</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45926</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>45470</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45938</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45098</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45608</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>44894</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45321</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45315</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>45077</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45077</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>46177</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45566</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>44991</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45022</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45812</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45254</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>44963</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46181</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45727</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45394</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45180</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>45379</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>45282</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45465</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45544</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45119</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45343</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45668</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>46055</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45902</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>46041</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45586</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45712</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44923</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45414</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45334</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45646</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45334</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>44972</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45303</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46198</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>45476</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>45525</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45716</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>45043</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46202</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45197</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>46112</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45474</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45253</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>44767</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>44732</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>44995</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>45106</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>44596</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>44992</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46212</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>46212</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>46212</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46212</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>46214</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45165</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>46218</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>45149</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>45182</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>46217</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45247</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>46222</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54963,7 +54963,7 @@
         <v>45310</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55036,7 +55036,7 @@
         <v>45110</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55109,7 +55109,7 @@
         <v>46223</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>44933</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45685</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>46135</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>46237</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>46205</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45278</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45278</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45506</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45141</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45141</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>44858</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45738</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>45090</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45121</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45738</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56355,7 +56355,7 @@
         <v>45738</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         <v>45566</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>45357</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>45622</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45189</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45387</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>46284</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46287</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>44991</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>44907</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>46287</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57178,7 +57178,7 @@
         <v>45275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45119</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>44694</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57402,7 +57402,7 @@
         <v>44946</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46287</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45737</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46288</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>45776</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>46287</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>46250</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45443</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45574</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>46290</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45414</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>46250</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>45357</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58371,7 +58371,7 @@
         <v>45370</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45603</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45217</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>45233</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>45700</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58736,7 +58736,7 @@
         <v>45183</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45517</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>45498</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45015</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46296</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45533</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45797</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>46190</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59325,7 +59325,7 @@
         <v>46253</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>46295</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>46253</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>46253</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>46253</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>46255</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>46300</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46256</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>46006</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>46300</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>46300</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>46300</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46260</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46260</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>46261</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>46189</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>46308</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>46308</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>46272</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>46272</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>46271</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>46271</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>46271</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46271</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46314</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>46272</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46310</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>46273</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>46314</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>46276</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46289</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46276</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46276</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46276</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>46244</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>46321</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>46280</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>46321</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62212,7 +62212,7 @@
         <v>46310</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46327</v>
+     